--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79EB69C-1AE0-49DA-8C75-DB546431B4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A654C2F-7E7F-4DB9-AB11-44CFB24F5F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72540" yWindow="825" windowWidth="27915" windowHeight="18855" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="8475" yWindow="2865" windowWidth="31350" windowHeight="19110" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
   <si>
     <t>год</t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>Черниговская</t>
+  </si>
+  <si>
+    <t>Семиреченская обл.</t>
   </si>
 </sst>
 </file>
@@ -568,9 +571,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E727C47-D865-4836-8CF2-7B9647F06C78}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -582,16 +585,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U91"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:U93"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.83984375" customWidth="1"/>
-    <col min="3" max="3" width="11.68359375" customWidth="1"/>
-    <col min="4" max="5" width="18.26171875" customWidth="1"/>
-    <col min="6" max="6" width="16.68359375" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
@@ -611,7 +614,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -627,7 +630,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -643,7 +646,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -657,7 +660,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -671,7 +674,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -685,7 +688,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -701,7 +704,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -715,7 +718,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -731,7 +734,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -747,7 +750,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -762,7 +765,7 @@
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -777,7 +780,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -792,7 +795,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -805,7 +808,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -820,7 +823,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -833,7 +836,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -846,7 +849,7 @@
       </c>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -857,7 +860,7 @@
         <v>52166</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -871,7 +874,7 @@
         <v>28698</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -884,7 +887,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -899,7 +902,7 @@
       </c>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -912,7 +915,7 @@
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -924,7 +927,7 @@
       </c>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -937,7 +940,7 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -950,7 +953,7 @@
       </c>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -962,451 +965,457 @@
       </c>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="7">
+        <v>1886</v>
+      </c>
+      <c r="C27" s="2">
+        <v>20065</v>
+      </c>
+      <c r="D27" s="8">
+        <v>12678</v>
+      </c>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="7">
+        <v>1887</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20264</v>
+      </c>
+      <c r="D28" s="8">
+        <v>14329</v>
+      </c>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B29" s="7">
         <v>1882</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D29" s="8">
         <v>15122</v>
       </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B30" s="7">
         <v>1911</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
+      <c r="C30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B31" s="7">
         <v>1895</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
+      <c r="C31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B32" s="7">
         <v>1889</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B33" s="7">
         <v>1901</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C33" s="2">
         <v>103114</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F33" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B34" s="7">
         <v>1881</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C34" s="2">
         <v>88569</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2">
-        <v>5330</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="2">
-        <v>5235</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>13</v>
       </c>
       <c r="B35" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1881</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2">
+        <v>5330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>13</v>
       </c>
       <c r="B36" s="7">
-        <v>1907</v>
+        <v>1882</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="D36" s="2">
+        <v>5235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>13</v>
       </c>
       <c r="B37" s="7">
+        <v>1904</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="7">
+        <v>1907</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="7">
         <v>1913</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E38" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F38" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E39" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F39" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
       <c r="B40" s="7">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="E40" s="2">
-        <v>603000</v>
+        <v>575000</v>
       </c>
       <c r="F40" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>30</v>
       </c>
       <c r="B41" s="7">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="E41" s="2">
-        <v>618000</v>
+        <v>589000</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="7">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="E42" s="2">
-        <v>633000</v>
+        <v>603000</v>
       </c>
       <c r="F42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="7">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="E43" s="2">
-        <v>648000</v>
+        <v>618000</v>
       </c>
       <c r="F43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="7">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="E44" s="2">
-        <v>664000</v>
+        <v>633000</v>
       </c>
       <c r="F44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="7">
+        <v>1886</v>
+      </c>
+      <c r="E45" s="2">
+        <v>648000</v>
+      </c>
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E46" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>32</v>
-      </c>
-      <c r="B45" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C45" s="2">
-        <v>100871</v>
-      </c>
-      <c r="D45" s="2">
-        <v>79202</v>
-      </c>
-      <c r="E45" s="2">
-        <v>2472605</v>
-      </c>
-      <c r="F45" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="7"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
-        <v>40</v>
       </c>
       <c r="B47" s="7">
         <v>1914</v>
       </c>
       <c r="C47" s="2">
-        <v>60509</v>
+        <v>100871</v>
       </c>
       <c r="D47" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E47" s="2"/>
+        <v>79202</v>
+      </c>
+      <c r="E47" s="2">
+        <v>2472605</v>
+      </c>
       <c r="F47" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C48" s="2">
-        <v>62023</v>
-      </c>
-      <c r="D48" s="2">
-        <v>35541</v>
-      </c>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="7"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="7">
         <v>1914</v>
       </c>
       <c r="C49" s="2">
-        <v>51346</v>
+        <v>60509</v>
       </c>
       <c r="D49" s="2">
-        <v>31414</v>
+        <v>34087</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B50" s="7">
         <v>1914</v>
       </c>
       <c r="C50" s="2">
-        <v>14341</v>
+        <v>62023</v>
       </c>
       <c r="D50" s="2">
-        <v>11957</v>
+        <v>35541</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B51" s="7">
         <v>1914</v>
       </c>
       <c r="C51" s="2">
-        <v>142692</v>
+        <v>51346</v>
       </c>
       <c r="D51" s="2">
-        <v>82123</v>
+        <v>31414</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="7"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C52" s="2">
+        <v>14341</v>
+      </c>
+      <c r="D52" s="2">
+        <v>11957</v>
+      </c>
       <c r="E52" s="2"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="7"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="F52" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C53" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D53" s="2">
+        <v>82123</v>
+      </c>
       <c r="E53" s="2"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="1" t="s">
+      <c r="F53" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B54" s="7"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B55" s="7"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="2"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="2"/>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
       <c r="O65" s="3"/>
       <c r="P65" s="2"/>
     </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="G66" s="2"/>
@@ -1418,41 +1427,41 @@
       <c r="O66" s="3"/>
       <c r="P66" s="2"/>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
       <c r="O67" s="3"/>
       <c r="P67" s="2"/>
     </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="O68" s="3"/>
       <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="O69" s="3"/>
+      <c r="P69" s="2"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="G70" s="2"/>
@@ -1462,8 +1471,13 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="O70" s="3"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="T70" s="2"/>
+      <c r="U70" s="2"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="G71" s="2"/>
@@ -1471,47 +1485,46 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
     </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
       <c r="L74" s="2"/>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M74" s="2"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="G76" s="2"/>
@@ -1521,27 +1534,27 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-    </row>
-    <row r="78" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="G79" s="2"/>
@@ -1551,16 +1564,17 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+    </row>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="G81" s="2"/>
@@ -1569,25 +1583,20 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
-      <c r="O81" s="2"/>
-    </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
+      <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
       <c r="O82" s="2"/>
     </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
+      <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
@@ -1595,31 +1604,55 @@
       <c r="L83" s="2"/>
       <c r="O83" s="2"/>
     </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
+    <row r="84" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
       <c r="O84" s="2"/>
     </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
       <c r="O85" s="2"/>
     </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
       <c r="O86" s="2"/>
     </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O87" s="2"/>
     </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O88" s="2"/>
     </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O89" s="2"/>
     </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O90" s="2"/>
     </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O91" s="2"/>
+    </row>
+    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O92" s="2"/>
+    </row>
+    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O93" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A654C2F-7E7F-4DB9-AB11-44CFB24F5F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739D7B5F-E9AF-4878-8EDB-A62DD41A48C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8475" yWindow="2865" windowWidth="31350" windowHeight="19110" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="54">
   <si>
     <t>год</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>Семиреченская обл.</t>
+  </si>
+  <si>
+    <t>Приморская обл.</t>
   </si>
 </sst>
 </file>
@@ -571,9 +574,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E727C47-D865-4836-8CF2-7B9647F06C78}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -585,16 +588,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U94"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.26171875" customWidth="1"/>
+    <col min="3" max="3" width="11.68359375" customWidth="1"/>
+    <col min="4" max="5" width="18.26171875" customWidth="1"/>
+    <col min="6" max="6" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
@@ -614,7 +617,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -630,7 +633,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -646,7 +649,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -660,7 +663,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -674,7 +677,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -688,7 +691,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -704,7 +707,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -718,7 +721,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -734,7 +737,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -750,7 +753,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -765,7 +768,7 @@
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -780,7 +783,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -795,7 +798,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -808,7 +811,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -823,7 +826,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -836,7 +839,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -849,7 +852,7 @@
       </c>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -860,7 +863,7 @@
         <v>52166</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -874,7 +877,7 @@
         <v>28698</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -887,7 +890,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -902,228 +905,228 @@
       </c>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="7">
+        <v>1896</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B23" s="7">
         <v>1889</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="8">
+      <c r="C23" s="4"/>
+      <c r="D23" s="8">
         <v>18552</v>
       </c>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B24" s="7">
         <v>1898</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C24" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="8">
-        <v>16816</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C25" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="7">
+        <v>1886</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="8">
+        <v>16816</v>
+      </c>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="7">
         <v>1892</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D27" s="8">
         <v>19117</v>
       </c>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C27" s="2">
-        <v>20065</v>
-      </c>
-      <c r="D27" s="8">
-        <v>12678</v>
-      </c>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>52</v>
       </c>
       <c r="B28" s="7">
+        <v>1886</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20065</v>
+      </c>
+      <c r="D28" s="8">
+        <v>12678</v>
+      </c>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="7">
         <v>1887</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C29" s="2">
         <v>20264</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D29" s="8">
         <v>14329</v>
       </c>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B30" s="7">
         <v>1882</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D30" s="8">
         <v>15122</v>
       </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B31" s="7">
         <v>1911</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="C31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B32" s="7">
         <v>1895</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B33" s="7">
         <v>1889</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="C33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B34" s="7">
         <v>1901</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C34" s="2">
         <v>103114</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
         <v>51</v>
-      </c>
-      <c r="B34" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C34" s="2">
-        <v>88569</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>13</v>
       </c>
       <c r="B35" s="7">
         <v>1881</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2">
-        <v>5330</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <v>88569</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>13</v>
       </c>
       <c r="B36" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1881</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" s="2">
-        <v>5235</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5330</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>13</v>
       </c>
       <c r="B37" s="7">
-        <v>1904</v>
+        <v>1882</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D37" s="2">
+        <v>5235</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>13</v>
       </c>
       <c r="B38" s="7">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>20</v>
@@ -1133,301 +1136,304 @@
       </c>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="7">
+        <v>1907</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="7">
         <v>1913</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E40" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>30</v>
       </c>
       <c r="B41" s="7">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E41" s="2">
-        <v>589000</v>
+        <v>575000</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="7">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E42" s="2">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="F42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="7">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E43" s="2">
-        <v>618000</v>
+        <v>603000</v>
       </c>
       <c r="F43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="7">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E44" s="2">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="F44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>30</v>
       </c>
       <c r="B45" s="7">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E45" s="2">
-        <v>648000</v>
+        <v>633000</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>30</v>
       </c>
       <c r="B46" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E46" s="2">
-        <v>664000</v>
+        <v>648000</v>
       </c>
       <c r="F46" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E47" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B48" s="7">
         <v>1914</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C48" s="2">
         <v>100871</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D48" s="2">
         <v>79202</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E48" s="2">
         <v>2472605</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F48" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="7"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="7"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
         <v>40</v>
-      </c>
-      <c r="B49" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C49" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D49" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>39</v>
       </c>
       <c r="B50" s="7">
         <v>1914</v>
       </c>
       <c r="C50" s="2">
-        <v>62023</v>
+        <v>60509</v>
       </c>
       <c r="D50" s="2">
-        <v>35541</v>
+        <v>34087</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B51" s="7">
         <v>1914</v>
       </c>
       <c r="C51" s="2">
-        <v>51346</v>
+        <v>62023</v>
       </c>
       <c r="D51" s="2">
-        <v>31414</v>
+        <v>35541</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B52" s="7">
         <v>1914</v>
       </c>
       <c r="C52" s="2">
-        <v>14341</v>
+        <v>51346</v>
       </c>
       <c r="D52" s="2">
-        <v>11957</v>
+        <v>31414</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" s="7">
         <v>1914</v>
       </c>
       <c r="C53" s="2">
-        <v>142692</v>
+        <v>14341</v>
       </c>
       <c r="D53" s="2">
-        <v>82123</v>
+        <v>11957</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="7"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C54" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D54" s="2">
+        <v>82123</v>
+      </c>
       <c r="E54" s="2"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F54" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="7"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="7"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
         <v>24</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="2"/>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
       <c r="O66" s="3"/>
       <c r="P66" s="2"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="G67" s="2"/>
@@ -1439,7 +1445,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="2"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="G68" s="2"/>
@@ -1451,80 +1457,82 @@
       <c r="O68" s="3"/>
       <c r="P68" s="2"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
       <c r="O69" s="3"/>
       <c r="P69" s="2"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
       <c r="O70" s="3"/>
       <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="T70" s="2"/>
-      <c r="U70" s="2"/>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="T71" s="2"/>
+      <c r="U71" s="2"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
       <c r="L75" s="2"/>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M75" s="2"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="G76" s="2"/>
@@ -1534,27 +1542,27 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="G79" s="2"/>
@@ -1564,51 +1572,49 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-    </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
-    </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+    </row>
+    <row r="82" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
-      <c r="O82" s="2"/>
-    </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+    </row>
+    <row r="83" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
       <c r="O83" s="2"/>
     </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
+      <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
@@ -1616,7 +1622,7 @@
       <c r="L84" s="2"/>
       <c r="O84" s="2"/>
     </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -1628,31 +1634,43 @@
       <c r="L85" s="2"/>
       <c r="O85" s="2"/>
     </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
+    <row r="86" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
       <c r="O86" s="2"/>
     </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
       <c r="O87" s="2"/>
     </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O88" s="2"/>
     </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O89" s="2"/>
     </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O90" s="2"/>
     </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O91" s="2"/>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O92" s="2"/>
     </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O93" s="2"/>
+    </row>
+    <row r="94" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O94" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739D7B5F-E9AF-4878-8EDB-A62DD41A48C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D855634B-98D9-4A50-AB65-DBFD64B54775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="55">
   <si>
     <t>год</t>
   </si>
@@ -194,6 +194,9 @@
   </si>
   <si>
     <t>Приморская обл.</t>
+  </si>
+  <si>
+    <t>Кутаисская</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U94"/>
+  <dimension ref="A1:U95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -828,15 +831,15 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B16" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="8">
-        <v>23374</v>
-      </c>
+        <v>1902</v>
+      </c>
+      <c r="C16" s="8">
+        <v>31115</v>
+      </c>
+      <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -844,11 +847,11 @@
         <v>7</v>
       </c>
       <c r="B17" s="7">
-        <v>1889</v>
+        <v>1882</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="8">
-        <v>29004</v>
+        <v>23374</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -857,24 +860,23 @@
         <v>7</v>
       </c>
       <c r="B18" s="7">
-        <v>1898</v>
-      </c>
-      <c r="C18" s="2">
-        <v>52166</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="8">
+        <v>29004</v>
+      </c>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" s="7">
-        <v>1889</v>
+        <v>1898</v>
       </c>
       <c r="C19" s="2">
-        <v>47652</v>
-      </c>
-      <c r="D19" s="2">
-        <v>28698</v>
+        <v>52166</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -882,80 +884,81 @@
         <v>8</v>
       </c>
       <c r="B20" s="7">
-        <v>1899</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C20" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D20" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>1899</v>
+      </c>
+      <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="B22" s="7">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B23" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="8">
-        <v>18552</v>
+        <v>1896</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B24" s="7">
-        <v>1898</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>27</v>
+        <v>1889</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="8">
+        <v>18552</v>
       </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B25" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C25" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D25" s="4"/>
+        <v>1898</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -963,12 +966,12 @@
         <v>36</v>
       </c>
       <c r="B26" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="8">
-        <v>16816</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C26" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -976,25 +979,23 @@
         <v>36</v>
       </c>
       <c r="B27" s="7">
-        <v>1892</v>
-      </c>
+        <v>1886</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" s="8">
-        <v>19117</v>
+        <v>16816</v>
       </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B28" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C28" s="2">
-        <v>20065</v>
+        <v>1892</v>
       </c>
       <c r="D28" s="8">
-        <v>12678</v>
+        <v>19117</v>
       </c>
       <c r="E28" s="4"/>
     </row>
@@ -1003,49 +1004,49 @@
         <v>52</v>
       </c>
       <c r="B29" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="C29" s="2">
-        <v>20264</v>
+        <v>20065</v>
       </c>
       <c r="D29" s="8">
-        <v>14329</v>
+        <v>12678</v>
       </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B30" s="7">
-        <v>1882</v>
+        <v>1887</v>
+      </c>
+      <c r="C30" s="2">
+        <v>20264</v>
       </c>
       <c r="D30" s="8">
-        <v>15122</v>
+        <v>14329</v>
       </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B31" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>20</v>
+        <v>1882</v>
+      </c>
+      <c r="D31" s="8">
+        <v>15122</v>
       </c>
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B32" s="7">
-        <v>1895</v>
+        <v>1911</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>20</v>
@@ -1057,10 +1058,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B33" s="7">
-        <v>1889</v>
+        <v>1895</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>20</v>
@@ -1072,39 +1073,42 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B34" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C34" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F34" t="s">
-        <v>25</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B35" s="7">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="C35" s="2">
-        <v>88569</v>
+        <v>103114</v>
+      </c>
+      <c r="F35" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B36" s="7">
         <v>1881</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2">
-        <v>5330</v>
+      <c r="C36" s="2">
+        <v>88569</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1112,13 +1116,11 @@
         <v>13</v>
       </c>
       <c r="B37" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1881</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" s="2">
-        <v>5235</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1126,22 +1128,21 @@
         <v>13</v>
       </c>
       <c r="B38" s="7">
-        <v>1904</v>
+        <v>1882</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="4"/>
+      <c r="D38" s="2">
+        <v>5235</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="7">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>20</v>
@@ -1156,7 +1157,7 @@
         <v>13</v>
       </c>
       <c r="B40" s="7">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>20</v>
@@ -1168,27 +1169,28 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B41" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E41" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F41" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="4"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="7">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E42" s="2">
-        <v>589000</v>
+        <v>575000</v>
       </c>
       <c r="F42" t="s">
         <v>31</v>
@@ -1199,10 +1201,10 @@
         <v>30</v>
       </c>
       <c r="B43" s="7">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E43" s="2">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="F43" t="s">
         <v>31</v>
@@ -1213,10 +1215,10 @@
         <v>30</v>
       </c>
       <c r="B44" s="7">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E44" s="2">
-        <v>618000</v>
+        <v>603000</v>
       </c>
       <c r="F44" t="s">
         <v>31</v>
@@ -1227,10 +1229,10 @@
         <v>30</v>
       </c>
       <c r="B45" s="7">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E45" s="2">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -1241,10 +1243,10 @@
         <v>30</v>
       </c>
       <c r="B46" s="7">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E46" s="2">
-        <v>648000</v>
+        <v>633000</v>
       </c>
       <c r="F46" t="s">
         <v>31</v>
@@ -1255,10 +1257,10 @@
         <v>30</v>
       </c>
       <c r="B47" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E47" s="2">
-        <v>664000</v>
+        <v>648000</v>
       </c>
       <c r="F47" t="s">
         <v>31</v>
@@ -1266,60 +1268,56 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E48" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B49" s="7">
         <v>1914</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C49" s="2">
         <v>100871</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D49" s="2">
         <v>79202</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E49" s="2">
         <v>2472605</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F49" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="7"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-    </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C50" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D50" s="2">
-        <v>34087</v>
-      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B51" s="7">
         <v>1914</v>
       </c>
       <c r="C51" s="2">
-        <v>62023</v>
+        <v>60509</v>
       </c>
       <c r="D51" s="2">
-        <v>35541</v>
+        <v>34087</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s">
@@ -1328,16 +1326,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B52" s="7">
         <v>1914</v>
       </c>
       <c r="C52" s="2">
-        <v>51346</v>
+        <v>62023</v>
       </c>
       <c r="D52" s="2">
-        <v>31414</v>
+        <v>35541</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s">
@@ -1346,16 +1344,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B53" s="7">
         <v>1914</v>
       </c>
       <c r="C53" s="2">
-        <v>14341</v>
+        <v>51346</v>
       </c>
       <c r="D53" s="2">
-        <v>11957</v>
+        <v>31414</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s">
@@ -1364,16 +1362,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B54" s="7">
         <v>1914</v>
       </c>
       <c r="C54" s="2">
-        <v>142692</v>
+        <v>14341</v>
       </c>
       <c r="D54" s="2">
-        <v>82123</v>
+        <v>11957</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s">
@@ -1381,10 +1379,22 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="7"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="A55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C55" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D55" s="2">
+        <v>82123</v>
+      </c>
       <c r="E55" s="2"/>
+      <c r="F55" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="7"/>
@@ -1392,56 +1402,50 @@
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="1" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="7"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
         <v>24</v>
       </c>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="2"/>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
       <c r="O67" s="3"/>
       <c r="P67" s="2"/>
     </row>
@@ -1476,6 +1480,8 @@
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
       <c r="O70" s="3"/>
       <c r="P70" s="2"/>
     </row>
@@ -1486,14 +1492,8 @@
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
       <c r="O71" s="3"/>
       <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="T71" s="2"/>
-      <c r="U71" s="2"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="2"/>
@@ -1502,6 +1502,14 @@
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="2"/>
@@ -1510,9 +1518,6 @@
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="2"/>
@@ -1521,6 +1526,9 @@
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="2"/>
@@ -1529,8 +1537,6 @@
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="2"/>
@@ -1539,8 +1545,8 @@
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
       <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="2"/>
@@ -1559,8 +1565,8 @@
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="2"/>
@@ -1569,8 +1575,8 @@
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="2"/>
@@ -1589,8 +1595,8 @@
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="2"/>
@@ -1599,8 +1605,8 @@
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
     </row>
     <row r="83" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="2"/>
@@ -1609,7 +1615,8 @@
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
-      <c r="O83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
     </row>
     <row r="84" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="2"/>
@@ -1618,15 +1625,12 @@
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
       <c r="O84" s="2"/>
     </row>
     <row r="85" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
+      <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
@@ -1647,11 +1651,20 @@
       <c r="O86" s="2"/>
     </row>
     <row r="87" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
       <c r="O87" s="2"/>
     </row>
     <row r="88" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
       <c r="O88" s="2"/>
     </row>
     <row r="89" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1671,6 +1684,9 @@
     </row>
     <row r="94" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O94" s="2"/>
+    </row>
+    <row r="95" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O95" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D855634B-98D9-4A50-AB65-DBFD64B54775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6539C8F1-FA9E-480A-9F7B-8182552C02E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
   <si>
     <t>год</t>
   </si>
@@ -197,6 +197,9 @@
   </si>
   <si>
     <t>Кутаисская</t>
+  </si>
+  <si>
+    <t>Томская</t>
   </si>
 </sst>
 </file>
@@ -244,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -261,6 +264,12 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,7 +600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U95"/>
+  <dimension ref="A1:U110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -1056,637 +1065,856 @@
       </c>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="9">
+        <v>1881</v>
+      </c>
+      <c r="C33" s="10">
+        <v>49210</v>
+      </c>
+      <c r="D33" s="10">
+        <v>28501</v>
+      </c>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="9">
+        <v>1882</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10">
+        <v>35470</v>
+      </c>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="9">
+        <v>1883</v>
+      </c>
+      <c r="C35" s="10">
+        <v>60508</v>
+      </c>
+      <c r="D35" s="10">
+        <v>34538</v>
+      </c>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="9">
+        <v>1885</v>
+      </c>
+      <c r="C36" s="10">
+        <v>62341</v>
+      </c>
+      <c r="D36" s="10">
+        <v>34345</v>
+      </c>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="9">
+        <v>1886</v>
+      </c>
+      <c r="C37" s="10">
+        <v>62210</v>
+      </c>
+      <c r="D37" s="10">
+        <v>34249</v>
+      </c>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="9">
+        <v>1887</v>
+      </c>
+      <c r="C38" s="10">
+        <v>64897</v>
+      </c>
+      <c r="D38" s="10">
+        <v>31536</v>
+      </c>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="9">
+        <v>1888</v>
+      </c>
+      <c r="C39" s="10">
+        <v>67462</v>
+      </c>
+      <c r="D39" s="10">
+        <v>39784</v>
+      </c>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="9">
+        <v>1889</v>
+      </c>
+      <c r="C40" s="10">
+        <v>67604</v>
+      </c>
+      <c r="D40" s="10">
+        <v>38492</v>
+      </c>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="9">
+        <v>1890</v>
+      </c>
+      <c r="C41" s="10">
+        <v>69629</v>
+      </c>
+      <c r="D41" s="10">
+        <v>39201</v>
+      </c>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="9">
+        <v>1892</v>
+      </c>
+      <c r="C42" s="10">
+        <v>77946</v>
+      </c>
+      <c r="D42" s="10"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" s="9">
+        <v>1895</v>
+      </c>
+      <c r="C43" s="10">
+        <v>87026</v>
+      </c>
+      <c r="D43" s="10">
+        <v>50346</v>
+      </c>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="9">
+        <v>1896</v>
+      </c>
+      <c r="C44" s="10">
+        <v>97843</v>
+      </c>
+      <c r="D44" s="10">
+        <v>57231</v>
+      </c>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="9">
+        <v>1902</v>
+      </c>
+      <c r="C45" s="10">
+        <v>117750</v>
+      </c>
+      <c r="D45" s="10">
+        <v>65540</v>
+      </c>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="9">
+        <v>1905</v>
+      </c>
+      <c r="C46" s="10">
+        <v>113188</v>
+      </c>
+      <c r="D46" s="10">
+        <v>76176</v>
+      </c>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="9">
+        <v>1910</v>
+      </c>
+      <c r="C47" s="10">
+        <v>209694</v>
+      </c>
+      <c r="D47" s="10"/>
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B48" s="7">
         <v>1895</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C35" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C36" s="2">
-        <v>88569</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2">
-        <v>5330</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="2">
-        <v>5235</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="7">
-        <v>1907</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="7">
-        <v>1913</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E42" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F42" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E43" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F43" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B44" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E44" s="2">
-        <v>603000</v>
-      </c>
-      <c r="F44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" s="7">
-        <v>1884</v>
-      </c>
-      <c r="E45" s="2">
-        <v>618000</v>
-      </c>
-      <c r="F45" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="7">
-        <v>1885</v>
-      </c>
-      <c r="E46" s="2">
-        <v>633000</v>
-      </c>
-      <c r="F46" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="7">
-        <v>1886</v>
-      </c>
-      <c r="E47" s="2">
-        <v>648000</v>
-      </c>
-      <c r="F47" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" s="7">
-        <v>1887</v>
-      </c>
-      <c r="E48" s="2">
-        <v>664000</v>
-      </c>
-      <c r="F48" t="s">
-        <v>31</v>
-      </c>
+      <c r="C48" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B49" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C49" s="2">
-        <v>100871</v>
-      </c>
-      <c r="D49" s="2">
-        <v>79202</v>
-      </c>
-      <c r="E49" s="2">
-        <v>2472605</v>
-      </c>
-      <c r="F49" t="s">
-        <v>45</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="4"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="7"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="7">
+        <v>1901</v>
+      </c>
+      <c r="C50" s="2">
+        <v>103114</v>
+      </c>
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B51" s="7">
-        <v>1914</v>
+        <v>1881</v>
       </c>
       <c r="C51" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D51" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s">
-        <v>44</v>
+        <v>88569</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B52" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C52" s="2">
-        <v>62023</v>
-      </c>
+        <v>1881</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" s="2">
-        <v>35541</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s">
-        <v>44</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B53" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C53" s="2">
-        <v>51346</v>
+        <v>1882</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D53" s="2">
-        <v>31414</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s">
-        <v>44</v>
+        <v>5235</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B54" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C54" s="2">
-        <v>14341</v>
-      </c>
-      <c r="D54" s="2">
-        <v>11957</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s">
-        <v>44</v>
-      </c>
+        <v>1904</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="4"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B55" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C55" s="2">
-        <v>142692</v>
-      </c>
-      <c r="D55" s="2">
-        <v>82123</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s">
-        <v>44</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="7"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
+      <c r="A56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" s="7">
+        <v>1913</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="4"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="7"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
+      <c r="A57" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="7">
+        <v>1881</v>
+      </c>
+      <c r="E57" s="2">
+        <v>575000</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" s="7">
+        <v>1882</v>
+      </c>
+      <c r="E58" s="2">
+        <v>589000</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="1" t="s">
-        <v>15</v>
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" s="7">
+        <v>1883</v>
+      </c>
+      <c r="E59" s="2">
+        <v>603000</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" s="7">
+        <v>1884</v>
+      </c>
+      <c r="E60" s="2">
+        <v>618000</v>
+      </c>
+      <c r="F60" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="B61" s="7">
+        <v>1885</v>
+      </c>
+      <c r="E61" s="2">
+        <v>633000</v>
+      </c>
+      <c r="F61" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="B62" s="7">
+        <v>1886</v>
+      </c>
+      <c r="E62" s="2">
+        <v>648000</v>
+      </c>
+      <c r="F62" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E63" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F63" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C64" s="2">
+        <v>100871</v>
+      </c>
+      <c r="D64" s="2">
+        <v>79202</v>
+      </c>
+      <c r="E64" s="2">
+        <v>2472605</v>
+      </c>
+      <c r="F64" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="7"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C66" s="2">
+        <v>60509</v>
+      </c>
+      <c r="D66" s="2">
+        <v>34087</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C67" s="2">
+        <v>62023</v>
+      </c>
+      <c r="D67" s="2">
+        <v>35541</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C68" s="2">
+        <v>51346</v>
+      </c>
+      <c r="D68" s="2">
+        <v>31414</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C69" s="2">
+        <v>14341</v>
+      </c>
+      <c r="D69" s="2">
+        <v>11957</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C70" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D70" s="2">
+        <v>82123</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="7"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="7"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" t="s">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" t="s">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
         <v>24</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="2"/>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="2"/>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="2"/>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="2"/>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="2"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="T72" s="2"/>
-      <c r="U72" s="2"/>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
-    </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-    </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O82" s="3"/>
+      <c r="P82" s="2"/>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
       <c r="L83" s="2"/>
-    </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="M83" s="2"/>
+      <c r="O83" s="3"/>
+      <c r="P83" s="2"/>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
-      <c r="O84" s="2"/>
-    </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="2"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
       <c r="L85" s="2"/>
-      <c r="O85" s="2"/>
-    </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="M85" s="2"/>
+      <c r="O85" s="3"/>
+      <c r="P85" s="2"/>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
+      <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-      <c r="L86" s="2"/>
-      <c r="O86" s="2"/>
-    </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O86" s="3"/>
+      <c r="P86" s="2"/>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
+      <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
-      <c r="O87" s="2"/>
-    </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-      <c r="O88" s="2"/>
-    </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O89" s="2"/>
-    </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O90" s="2"/>
-    </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O91" s="2"/>
-    </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O92" s="2"/>
-    </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O93" s="2"/>
-    </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O94" s="2"/>
-    </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O95" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="O87" s="3"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="2"/>
+      <c r="T87" s="2"/>
+      <c r="U87" s="2"/>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+    </row>
+    <row r="97" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+    </row>
+    <row r="98" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+    </row>
+    <row r="99" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="O99" s="2"/>
+    </row>
+    <row r="100" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="O100" s="2"/>
+    </row>
+    <row r="101" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+      <c r="O101" s="2"/>
+    </row>
+    <row r="102" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+      <c r="O102" s="2"/>
+    </row>
+    <row r="103" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
+      <c r="O103" s="2"/>
+    </row>
+    <row r="104" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O104" s="2"/>
+    </row>
+    <row r="105" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O105" s="2"/>
+    </row>
+    <row r="106" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O106" s="2"/>
+    </row>
+    <row r="107" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O107" s="2"/>
+    </row>
+    <row r="108" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O108" s="2"/>
+    </row>
+    <row r="109" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O109" s="2"/>
+    </row>
+    <row r="110" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O110" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6539C8F1-FA9E-480A-9F7B-8182552C02E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DFC071-01EB-4094-964D-560A1B0D752F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="61770" yWindow="735" windowWidth="39795" windowHeight="19950" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="56">
   <si>
     <t>год</t>
   </si>
@@ -600,7 +600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U110"/>
+  <dimension ref="A1:U111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -1203,12 +1203,14 @@
         <v>55</v>
       </c>
       <c r="B42" s="9">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="C42" s="10">
-        <v>77946</v>
-      </c>
-      <c r="D42" s="10"/>
+        <v>69629</v>
+      </c>
+      <c r="D42" s="10">
+        <v>39201</v>
+      </c>
       <c r="E42" s="4"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1216,14 +1218,12 @@
         <v>55</v>
       </c>
       <c r="B43" s="9">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="C43" s="10">
-        <v>87026</v>
-      </c>
-      <c r="D43" s="10">
-        <v>50346</v>
-      </c>
+        <v>77946</v>
+      </c>
+      <c r="D43" s="10"/>
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1231,13 +1231,13 @@
         <v>55</v>
       </c>
       <c r="B44" s="9">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="C44" s="10">
-        <v>97843</v>
+        <v>87026</v>
       </c>
       <c r="D44" s="10">
-        <v>57231</v>
+        <v>50346</v>
       </c>
       <c r="E44" s="4"/>
     </row>
@@ -1246,13 +1246,13 @@
         <v>55</v>
       </c>
       <c r="B45" s="9">
-        <v>1902</v>
+        <v>1896</v>
       </c>
       <c r="C45" s="10">
-        <v>117750</v>
+        <v>97843</v>
       </c>
       <c r="D45" s="10">
-        <v>65540</v>
+        <v>57231</v>
       </c>
       <c r="E45" s="4"/>
     </row>
@@ -1261,13 +1261,13 @@
         <v>55</v>
       </c>
       <c r="B46" s="9">
-        <v>1905</v>
+        <v>1902</v>
       </c>
       <c r="C46" s="10">
-        <v>113188</v>
+        <v>117750</v>
       </c>
       <c r="D46" s="10">
-        <v>76176</v>
+        <v>65540</v>
       </c>
       <c r="E46" s="4"/>
     </row>
@@ -1276,35 +1276,35 @@
         <v>55</v>
       </c>
       <c r="B47" s="9">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="C47" s="10">
-        <v>209694</v>
-      </c>
-      <c r="D47" s="10"/>
+        <v>113188</v>
+      </c>
+      <c r="D47" s="10">
+        <v>76176</v>
+      </c>
       <c r="E47" s="4"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="7">
-        <v>1895</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B48" s="9">
+        <v>1910</v>
+      </c>
+      <c r="C48" s="10">
+        <v>209694</v>
+      </c>
+      <c r="D48" s="10"/>
       <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>1889</v>
+        <v>1895</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>20</v>
@@ -1316,39 +1316,42 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B50" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C50" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F50" t="s">
-        <v>25</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="4"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B51" s="7">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="C51" s="2">
-        <v>88569</v>
+        <v>103114</v>
+      </c>
+      <c r="F51" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B52" s="7">
         <v>1881</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2">
-        <v>5330</v>
+      <c r="C52" s="2">
+        <v>88569</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1356,13 +1359,11 @@
         <v>13</v>
       </c>
       <c r="B53" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1881</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" s="2">
-        <v>5235</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1370,22 +1371,21 @@
         <v>13</v>
       </c>
       <c r="B54" s="7">
-        <v>1904</v>
+        <v>1882</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" s="4"/>
+      <c r="D54" s="2">
+        <v>5235</v>
+      </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>13</v>
       </c>
       <c r="B55" s="7">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>20</v>
@@ -1400,7 +1400,7 @@
         <v>13</v>
       </c>
       <c r="B56" s="7">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>20</v>
@@ -1412,27 +1412,28 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B57" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E57" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F57" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>30</v>
       </c>
       <c r="B58" s="7">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E58" s="2">
-        <v>589000</v>
+        <v>575000</v>
       </c>
       <c r="F58" t="s">
         <v>31</v>
@@ -1443,10 +1444,10 @@
         <v>30</v>
       </c>
       <c r="B59" s="7">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E59" s="2">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="F59" t="s">
         <v>31</v>
@@ -1457,10 +1458,10 @@
         <v>30</v>
       </c>
       <c r="B60" s="7">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E60" s="2">
-        <v>618000</v>
+        <v>603000</v>
       </c>
       <c r="F60" t="s">
         <v>31</v>
@@ -1471,10 +1472,10 @@
         <v>30</v>
       </c>
       <c r="B61" s="7">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E61" s="2">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -1485,10 +1486,10 @@
         <v>30</v>
       </c>
       <c r="B62" s="7">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E62" s="2">
-        <v>648000</v>
+        <v>633000</v>
       </c>
       <c r="F62" t="s">
         <v>31</v>
@@ -1499,10 +1500,10 @@
         <v>30</v>
       </c>
       <c r="B63" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E63" s="2">
-        <v>664000</v>
+        <v>648000</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -1510,60 +1511,56 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E64" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
         <v>32</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B65" s="7">
         <v>1914</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C65" s="2">
         <v>100871</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D65" s="2">
         <v>79202</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E65" s="2">
         <v>2472605</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F65" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="7"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-    </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C66" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D66" s="2">
-        <v>34087</v>
-      </c>
+      <c r="B66" s="7"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-      <c r="F66" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B67" s="7">
         <v>1914</v>
       </c>
       <c r="C67" s="2">
-        <v>62023</v>
+        <v>60509</v>
       </c>
       <c r="D67" s="2">
-        <v>35541</v>
+        <v>34087</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s">
@@ -1572,16 +1569,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B68" s="7">
         <v>1914</v>
       </c>
       <c r="C68" s="2">
-        <v>51346</v>
+        <v>62023</v>
       </c>
       <c r="D68" s="2">
-        <v>31414</v>
+        <v>35541</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s">
@@ -1590,16 +1587,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="7">
         <v>1914</v>
       </c>
       <c r="C69" s="2">
-        <v>14341</v>
+        <v>51346</v>
       </c>
       <c r="D69" s="2">
-        <v>11957</v>
+        <v>31414</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s">
@@ -1608,16 +1605,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B70" s="7">
         <v>1914</v>
       </c>
       <c r="C70" s="2">
-        <v>142692</v>
+        <v>14341</v>
       </c>
       <c r="D70" s="2">
-        <v>82123</v>
+        <v>11957</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s">
@@ -1625,10 +1622,22 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="7"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
+      <c r="A71" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C71" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D71" s="2">
+        <v>82123</v>
+      </c>
       <c r="E71" s="2"/>
+      <c r="F71" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="7"/>
@@ -1636,56 +1645,50 @@
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="1" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="7"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="O82" s="3"/>
-      <c r="P82" s="2"/>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
-      <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
       <c r="O83" s="3"/>
       <c r="P83" s="2"/>
     </row>
@@ -1720,6 +1723,8 @@
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
       <c r="O86" s="3"/>
       <c r="P86" s="2"/>
     </row>
@@ -1730,14 +1735,8 @@
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
       <c r="O87" s="3"/>
       <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-      <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="2"/>
@@ -1746,6 +1745,14 @@
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+      <c r="O88" s="3"/>
+      <c r="P88" s="2"/>
+      <c r="Q88" s="2"/>
+      <c r="T88" s="2"/>
+      <c r="U88" s="2"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="2"/>
@@ -1754,9 +1761,6 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="2"/>
@@ -1765,6 +1769,9 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="2"/>
@@ -1773,8 +1780,6 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="2"/>
@@ -1783,8 +1788,8 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
       <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="2"/>
@@ -1803,8 +1808,8 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="2"/>
@@ -1813,8 +1818,8 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="2"/>
@@ -1833,8 +1838,8 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
     </row>
     <row r="98" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="2"/>
@@ -1843,8 +1848,8 @@
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
-      <c r="L98" s="2"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
     </row>
     <row r="99" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="2"/>
@@ -1853,7 +1858,8 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
-      <c r="O99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
     </row>
     <row r="100" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="2"/>
@@ -1862,15 +1868,12 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
       <c r="O100" s="2"/>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
+      <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
@@ -1891,11 +1894,20 @@
       <c r="O102" s="2"/>
     </row>
     <row r="103" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
       <c r="O103" s="2"/>
     </row>
     <row r="104" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
       <c r="O104" s="2"/>
     </row>
     <row r="105" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1915,6 +1927,9 @@
     </row>
     <row r="110" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O110" s="2"/>
+    </row>
+    <row r="111" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O111" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DFC071-01EB-4094-964D-560A1B0D752F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238FD518-8740-4A13-A226-CDADE47BE27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61770" yWindow="735" windowWidth="39795" windowHeight="19950" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="59430" yWindow="1650" windowWidth="39795" windowHeight="19950" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="57">
   <si>
     <t>год</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>Томская</t>
+  </si>
+  <si>
+    <t>Оренбургская</t>
   </si>
 </sst>
 </file>
@@ -600,7 +603,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U111"/>
+  <dimension ref="A1:U112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -890,16 +893,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B20" s="7">
-        <v>1889</v>
+        <v>1881</v>
       </c>
       <c r="C20" s="2">
-        <v>47652</v>
+        <v>72106</v>
       </c>
       <c r="D20" s="2">
-        <v>28698</v>
+        <v>50444</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -907,80 +910,81 @@
         <v>8</v>
       </c>
       <c r="B21" s="7">
-        <v>1899</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C21" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D21" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>1899</v>
+      </c>
+      <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="B23" s="7">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B24" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="8">
-        <v>18552</v>
+        <v>1896</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B25" s="7">
-        <v>1898</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>27</v>
+        <v>1889</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="8">
+        <v>18552</v>
       </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B26" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C26" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D26" s="4"/>
+        <v>1898</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -988,12 +992,12 @@
         <v>36</v>
       </c>
       <c r="B27" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="8">
-        <v>16816</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C27" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D27" s="4"/>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1001,25 +1005,23 @@
         <v>36</v>
       </c>
       <c r="B28" s="7">
-        <v>1892</v>
-      </c>
+        <v>1886</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" s="8">
-        <v>19117</v>
+        <v>16816</v>
       </c>
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B29" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C29" s="2">
-        <v>20065</v>
+        <v>1892</v>
       </c>
       <c r="D29" s="8">
-        <v>12678</v>
+        <v>19117</v>
       </c>
       <c r="E29" s="4"/>
     </row>
@@ -1028,55 +1030,55 @@
         <v>52</v>
       </c>
       <c r="B30" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="C30" s="2">
-        <v>20264</v>
+        <v>20065</v>
       </c>
       <c r="D30" s="8">
-        <v>14329</v>
+        <v>12678</v>
       </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B31" s="7">
-        <v>1882</v>
+        <v>1887</v>
+      </c>
+      <c r="C31" s="2">
+        <v>20264</v>
       </c>
       <c r="D31" s="8">
-        <v>15122</v>
+        <v>14329</v>
       </c>
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B32" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>20</v>
+        <v>1882</v>
+      </c>
+      <c r="D32" s="8">
+        <v>15122</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="9">
-        <v>1881</v>
-      </c>
-      <c r="C33" s="10">
-        <v>49210</v>
-      </c>
-      <c r="D33" s="10">
-        <v>28501</v>
+        <v>11</v>
+      </c>
+      <c r="B33" s="7">
+        <v>1911</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E33" s="4"/>
     </row>
@@ -1085,11 +1087,13 @@
         <v>55</v>
       </c>
       <c r="B34" s="9">
-        <v>1882</v>
-      </c>
-      <c r="C34" s="10"/>
+        <v>1881</v>
+      </c>
+      <c r="C34" s="10">
+        <v>49210</v>
+      </c>
       <c r="D34" s="10">
-        <v>35470</v>
+        <v>28501</v>
       </c>
       <c r="E34" s="4"/>
     </row>
@@ -1098,13 +1102,11 @@
         <v>55</v>
       </c>
       <c r="B35" s="9">
-        <v>1883</v>
-      </c>
-      <c r="C35" s="10">
-        <v>60508</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C35" s="10"/>
       <c r="D35" s="10">
-        <v>34538</v>
+        <v>35470</v>
       </c>
       <c r="E35" s="4"/>
     </row>
@@ -1113,13 +1115,13 @@
         <v>55</v>
       </c>
       <c r="B36" s="9">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="C36" s="10">
-        <v>62341</v>
+        <v>60508</v>
       </c>
       <c r="D36" s="10">
-        <v>34345</v>
+        <v>34538</v>
       </c>
       <c r="E36" s="4"/>
     </row>
@@ -1128,13 +1130,13 @@
         <v>55</v>
       </c>
       <c r="B37" s="9">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="C37" s="10">
-        <v>62210</v>
+        <v>62341</v>
       </c>
       <c r="D37" s="10">
-        <v>34249</v>
+        <v>34345</v>
       </c>
       <c r="E37" s="4"/>
     </row>
@@ -1143,13 +1145,13 @@
         <v>55</v>
       </c>
       <c r="B38" s="9">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="C38" s="10">
-        <v>64897</v>
+        <v>62210</v>
       </c>
       <c r="D38" s="10">
-        <v>31536</v>
+        <v>34249</v>
       </c>
       <c r="E38" s="4"/>
     </row>
@@ -1158,13 +1160,13 @@
         <v>55</v>
       </c>
       <c r="B39" s="9">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="C39" s="10">
-        <v>67462</v>
+        <v>64897</v>
       </c>
       <c r="D39" s="10">
-        <v>39784</v>
+        <v>31536</v>
       </c>
       <c r="E39" s="4"/>
     </row>
@@ -1173,13 +1175,13 @@
         <v>55</v>
       </c>
       <c r="B40" s="9">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="C40" s="10">
-        <v>67604</v>
+        <v>67462</v>
       </c>
       <c r="D40" s="10">
-        <v>38492</v>
+        <v>39784</v>
       </c>
       <c r="E40" s="4"/>
     </row>
@@ -1188,13 +1190,13 @@
         <v>55</v>
       </c>
       <c r="B41" s="9">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="C41" s="10">
-        <v>69629</v>
+        <v>67604</v>
       </c>
       <c r="D41" s="10">
-        <v>39201</v>
+        <v>38492</v>
       </c>
       <c r="E41" s="4"/>
     </row>
@@ -1203,7 +1205,7 @@
         <v>55</v>
       </c>
       <c r="B42" s="9">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="C42" s="10">
         <v>69629</v>
@@ -1218,12 +1220,14 @@
         <v>55</v>
       </c>
       <c r="B43" s="9">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="C43" s="10">
-        <v>77946</v>
-      </c>
-      <c r="D43" s="10"/>
+        <v>69629</v>
+      </c>
+      <c r="D43" s="10">
+        <v>39201</v>
+      </c>
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1231,14 +1235,12 @@
         <v>55</v>
       </c>
       <c r="B44" s="9">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="C44" s="10">
-        <v>87026</v>
-      </c>
-      <c r="D44" s="10">
-        <v>50346</v>
-      </c>
+        <v>77946</v>
+      </c>
+      <c r="D44" s="10"/>
       <c r="E44" s="4"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1246,13 +1248,13 @@
         <v>55</v>
       </c>
       <c r="B45" s="9">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="C45" s="10">
-        <v>97843</v>
+        <v>87026</v>
       </c>
       <c r="D45" s="10">
-        <v>57231</v>
+        <v>50346</v>
       </c>
       <c r="E45" s="4"/>
     </row>
@@ -1261,13 +1263,13 @@
         <v>55</v>
       </c>
       <c r="B46" s="9">
-        <v>1902</v>
+        <v>1896</v>
       </c>
       <c r="C46" s="10">
-        <v>117750</v>
+        <v>97843</v>
       </c>
       <c r="D46" s="10">
-        <v>65540</v>
+        <v>57231</v>
       </c>
       <c r="E46" s="4"/>
     </row>
@@ -1276,13 +1278,13 @@
         <v>55</v>
       </c>
       <c r="B47" s="9">
-        <v>1905</v>
+        <v>1902</v>
       </c>
       <c r="C47" s="10">
-        <v>113188</v>
+        <v>117750</v>
       </c>
       <c r="D47" s="10">
-        <v>76176</v>
+        <v>65540</v>
       </c>
       <c r="E47" s="4"/>
     </row>
@@ -1291,35 +1293,35 @@
         <v>55</v>
       </c>
       <c r="B48" s="9">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="C48" s="10">
-        <v>209694</v>
-      </c>
-      <c r="D48" s="10"/>
+        <v>113188</v>
+      </c>
+      <c r="D48" s="10">
+        <v>76176</v>
+      </c>
       <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="7">
-        <v>1895</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B49" s="9">
+        <v>1910</v>
+      </c>
+      <c r="C49" s="10">
+        <v>209694</v>
+      </c>
+      <c r="D49" s="10"/>
       <c r="E49" s="4"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" s="7">
-        <v>1889</v>
+        <v>1895</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>20</v>
@@ -1331,39 +1333,42 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B51" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C51" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F51" t="s">
-        <v>25</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="4"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B52" s="7">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="C52" s="2">
-        <v>88569</v>
+        <v>103114</v>
+      </c>
+      <c r="F52" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B53" s="7">
         <v>1881</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2">
-        <v>5330</v>
+      <c r="C53" s="2">
+        <v>88569</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1371,13 +1376,11 @@
         <v>13</v>
       </c>
       <c r="B54" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1881</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" s="2">
-        <v>5235</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1385,22 +1388,21 @@
         <v>13</v>
       </c>
       <c r="B55" s="7">
-        <v>1904</v>
+        <v>1882</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" s="4"/>
+      <c r="D55" s="2">
+        <v>5235</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>13</v>
       </c>
       <c r="B56" s="7">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>20</v>
@@ -1415,7 +1417,7 @@
         <v>13</v>
       </c>
       <c r="B57" s="7">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>20</v>
@@ -1427,27 +1429,28 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B58" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E58" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F58" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="4"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>30</v>
       </c>
       <c r="B59" s="7">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E59" s="2">
-        <v>589000</v>
+        <v>575000</v>
       </c>
       <c r="F59" t="s">
         <v>31</v>
@@ -1458,10 +1461,10 @@
         <v>30</v>
       </c>
       <c r="B60" s="7">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E60" s="2">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="F60" t="s">
         <v>31</v>
@@ -1472,10 +1475,10 @@
         <v>30</v>
       </c>
       <c r="B61" s="7">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E61" s="2">
-        <v>618000</v>
+        <v>603000</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -1486,10 +1489,10 @@
         <v>30</v>
       </c>
       <c r="B62" s="7">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E62" s="2">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="F62" t="s">
         <v>31</v>
@@ -1500,10 +1503,10 @@
         <v>30</v>
       </c>
       <c r="B63" s="7">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E63" s="2">
-        <v>648000</v>
+        <v>633000</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -1514,10 +1517,10 @@
         <v>30</v>
       </c>
       <c r="B64" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E64" s="2">
-        <v>664000</v>
+        <v>648000</v>
       </c>
       <c r="F64" t="s">
         <v>31</v>
@@ -1525,60 +1528,56 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B65" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E65" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F65" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
         <v>32</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B66" s="7">
         <v>1914</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C66" s="2">
         <v>100871</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D66" s="2">
         <v>79202</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E66" s="2">
         <v>2472605</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F66" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="7"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-    </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C67" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D67" s="2">
-        <v>34087</v>
-      </c>
+      <c r="B67" s="7"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="F67" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B68" s="7">
         <v>1914</v>
       </c>
       <c r="C68" s="2">
-        <v>62023</v>
+        <v>60509</v>
       </c>
       <c r="D68" s="2">
-        <v>35541</v>
+        <v>34087</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s">
@@ -1587,16 +1586,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B69" s="7">
         <v>1914</v>
       </c>
       <c r="C69" s="2">
-        <v>51346</v>
+        <v>62023</v>
       </c>
       <c r="D69" s="2">
-        <v>31414</v>
+        <v>35541</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s">
@@ -1605,16 +1604,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B70" s="7">
         <v>1914</v>
       </c>
       <c r="C70" s="2">
-        <v>14341</v>
+        <v>51346</v>
       </c>
       <c r="D70" s="2">
-        <v>11957</v>
+        <v>31414</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s">
@@ -1623,16 +1622,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B71" s="7">
         <v>1914</v>
       </c>
       <c r="C71" s="2">
-        <v>142692</v>
+        <v>14341</v>
       </c>
       <c r="D71" s="2">
-        <v>82123</v>
+        <v>11957</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s">
@@ -1640,10 +1639,22 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="7"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
+      <c r="A72" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C72" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D72" s="2">
+        <v>82123</v>
+      </c>
       <c r="E72" s="2"/>
+      <c r="F72" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="7"/>
@@ -1651,56 +1662,50 @@
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="1" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="7"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" t="s">
         <v>24</v>
       </c>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="O83" s="3"/>
-      <c r="P83" s="2"/>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-      <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
       <c r="O84" s="3"/>
       <c r="P84" s="2"/>
     </row>
@@ -1735,6 +1740,8 @@
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
       <c r="O87" s="3"/>
       <c r="P87" s="2"/>
     </row>
@@ -1745,14 +1752,8 @@
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
       <c r="O88" s="3"/>
       <c r="P88" s="2"/>
-      <c r="Q88" s="2"/>
-      <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="2"/>
@@ -1761,6 +1762,14 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="O89" s="3"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" s="2"/>
+      <c r="T89" s="2"/>
+      <c r="U89" s="2"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="2"/>
@@ -1769,9 +1778,6 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="2"/>
@@ -1780,6 +1786,9 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="2"/>
@@ -1788,8 +1797,6 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="2"/>
@@ -1798,8 +1805,8 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
       <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="2"/>
@@ -1818,8 +1825,8 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="2"/>
@@ -1828,8 +1835,8 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
     </row>
     <row r="97" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="2"/>
@@ -1848,8 +1855,8 @@
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
     </row>
     <row r="99" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="2"/>
@@ -1858,8 +1865,8 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
-      <c r="L99" s="2"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
     </row>
     <row r="100" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="2"/>
@@ -1868,7 +1875,8 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
-      <c r="O100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="2"/>
@@ -1877,15 +1885,12 @@
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
-      <c r="L101" s="2"/>
       <c r="O101" s="2"/>
     </row>
     <row r="102" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
+      <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
@@ -1906,11 +1911,20 @@
       <c r="O103" s="2"/>
     </row>
     <row r="104" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
       <c r="O104" s="2"/>
     </row>
     <row r="105" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
       <c r="O105" s="2"/>
     </row>
     <row r="106" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1930,6 +1944,9 @@
     </row>
     <row r="111" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O111" s="2"/>
+    </row>
+    <row r="112" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O112" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238FD518-8740-4A13-A226-CDADE47BE27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63254AFF-479F-4A8A-8BB0-4162C1121BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59430" yWindow="1650" windowWidth="39795" windowHeight="19950" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="67020" yWindow="3960" windowWidth="39795" windowHeight="13170" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="57">
   <si>
     <t>год</t>
   </si>
@@ -603,7 +603,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U112"/>
+  <dimension ref="A1:U113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -1351,36 +1351,39 @@
         <v>12</v>
       </c>
       <c r="B52" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C52" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F52" t="s">
-        <v>25</v>
-      </c>
+        <v>1881</v>
+      </c>
+      <c r="C52" s="8">
+        <v>94421</v>
+      </c>
+      <c r="D52" s="8">
+        <v>73778</v>
+      </c>
+      <c r="E52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B53" s="7">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="C53" s="2">
-        <v>88569</v>
+        <v>103114</v>
+      </c>
+      <c r="F53" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B54" s="7">
         <v>1881</v>
       </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2">
-        <v>5330</v>
+      <c r="C54" s="2">
+        <v>88569</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1388,13 +1391,11 @@
         <v>13</v>
       </c>
       <c r="B55" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1881</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" s="2">
-        <v>5235</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1402,22 +1403,21 @@
         <v>13</v>
       </c>
       <c r="B56" s="7">
-        <v>1904</v>
+        <v>1882</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="4"/>
+      <c r="D56" s="2">
+        <v>5235</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>13</v>
       </c>
       <c r="B57" s="7">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>20</v>
@@ -1432,7 +1432,7 @@
         <v>13</v>
       </c>
       <c r="B58" s="7">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>20</v>
@@ -1444,27 +1444,28 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B59" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E59" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F59" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="4"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>30</v>
       </c>
       <c r="B60" s="7">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E60" s="2">
-        <v>589000</v>
+        <v>575000</v>
       </c>
       <c r="F60" t="s">
         <v>31</v>
@@ -1475,10 +1476,10 @@
         <v>30</v>
       </c>
       <c r="B61" s="7">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E61" s="2">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -1489,10 +1490,10 @@
         <v>30</v>
       </c>
       <c r="B62" s="7">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E62" s="2">
-        <v>618000</v>
+        <v>603000</v>
       </c>
       <c r="F62" t="s">
         <v>31</v>
@@ -1503,10 +1504,10 @@
         <v>30</v>
       </c>
       <c r="B63" s="7">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E63" s="2">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -1517,10 +1518,10 @@
         <v>30</v>
       </c>
       <c r="B64" s="7">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E64" s="2">
-        <v>648000</v>
+        <v>633000</v>
       </c>
       <c r="F64" t="s">
         <v>31</v>
@@ -1531,10 +1532,10 @@
         <v>30</v>
       </c>
       <c r="B65" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E65" s="2">
-        <v>664000</v>
+        <v>648000</v>
       </c>
       <c r="F65" t="s">
         <v>31</v>
@@ -1542,60 +1543,56 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
+        <v>30</v>
+      </c>
+      <c r="B66" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E66" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
         <v>32</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B67" s="7">
         <v>1914</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C67" s="2">
         <v>100871</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D67" s="2">
         <v>79202</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E67" s="2">
         <v>2472605</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F67" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="7"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-    </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C68" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D68" s="2">
-        <v>34087</v>
-      </c>
+      <c r="B68" s="7"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B69" s="7">
         <v>1914</v>
       </c>
       <c r="C69" s="2">
-        <v>62023</v>
+        <v>60509</v>
       </c>
       <c r="D69" s="2">
-        <v>35541</v>
+        <v>34087</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s">
@@ -1604,16 +1601,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B70" s="7">
         <v>1914</v>
       </c>
       <c r="C70" s="2">
-        <v>51346</v>
+        <v>62023</v>
       </c>
       <c r="D70" s="2">
-        <v>31414</v>
+        <v>35541</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s">
@@ -1622,16 +1619,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B71" s="7">
         <v>1914</v>
       </c>
       <c r="C71" s="2">
-        <v>14341</v>
+        <v>51346</v>
       </c>
       <c r="D71" s="2">
-        <v>11957</v>
+        <v>31414</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s">
@@ -1640,16 +1637,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B72" s="7">
         <v>1914</v>
       </c>
       <c r="C72" s="2">
-        <v>142692</v>
+        <v>14341</v>
       </c>
       <c r="D72" s="2">
-        <v>82123</v>
+        <v>11957</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s">
@@ -1657,10 +1654,22 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="7"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+      <c r="A73" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C73" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D73" s="2">
+        <v>82123</v>
+      </c>
       <c r="E73" s="2"/>
+      <c r="F73" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="7"/>
@@ -1668,56 +1677,50 @@
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="1" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="7"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" t="s">
         <v>24</v>
       </c>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="O84" s="3"/>
-      <c r="P84" s="2"/>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-      <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
       <c r="O85" s="3"/>
       <c r="P85" s="2"/>
     </row>
@@ -1752,6 +1755,8 @@
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
       <c r="O88" s="3"/>
       <c r="P88" s="2"/>
     </row>
@@ -1762,14 +1767,8 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
       <c r="O89" s="3"/>
       <c r="P89" s="2"/>
-      <c r="Q89" s="2"/>
-      <c r="T89" s="2"/>
-      <c r="U89" s="2"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="2"/>
@@ -1778,6 +1777,14 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="2"/>
+      <c r="T90" s="2"/>
+      <c r="U90" s="2"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="2"/>
@@ -1786,9 +1793,6 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="2"/>
@@ -1797,6 +1801,9 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="2"/>
@@ -1805,8 +1812,6 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="2"/>
@@ -1815,8 +1820,8 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
       <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="2"/>
@@ -1835,8 +1840,8 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
     </row>
     <row r="97" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="2"/>
@@ -1845,8 +1850,8 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
-      <c r="L97" s="2"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
     </row>
     <row r="98" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="2"/>
@@ -1865,8 +1870,8 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
     </row>
     <row r="100" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="2"/>
@@ -1875,8 +1880,8 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="2"/>
@@ -1885,7 +1890,8 @@
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
-      <c r="O101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
     </row>
     <row r="102" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="2"/>
@@ -1894,15 +1900,12 @@
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
       <c r="O102" s="2"/>
     </row>
     <row r="103" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
+      <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
@@ -1923,11 +1926,20 @@
       <c r="O104" s="2"/>
     </row>
     <row r="105" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
       <c r="O105" s="2"/>
     </row>
     <row r="106" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K106" s="6"/>
+      <c r="L106" s="6"/>
       <c r="O106" s="2"/>
     </row>
     <row r="107" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1947,6 +1959,9 @@
     </row>
     <row r="112" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O112" s="2"/>
+    </row>
+    <row r="113" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O113" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63254AFF-479F-4A8A-8BB0-4162C1121BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EDC357-0B80-4F2F-9F61-AF6767D6EC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67020" yWindow="3960" windowWidth="39795" windowHeight="13170" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="59">
   <si>
     <t>год</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>Оренбургская</t>
+  </si>
+  <si>
+    <t>г. Николаев</t>
+  </si>
+  <si>
+    <t>г. Одесса</t>
   </si>
 </sst>
 </file>
@@ -603,7 +609,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U113"/>
+  <dimension ref="A1:U115"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -893,123 +899,119 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="7">
-        <v>1881</v>
+        <v>1905</v>
       </c>
       <c r="C20" s="2">
-        <v>72106</v>
-      </c>
-      <c r="D20" s="2">
-        <v>50444</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B21" s="7">
-        <v>1889</v>
+        <v>1905</v>
       </c>
       <c r="C21" s="2">
-        <v>47652</v>
-      </c>
-      <c r="D21" s="2">
-        <v>28698</v>
+        <v>17694</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B22" s="7">
-        <v>1899</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="4"/>
+        <v>1881</v>
+      </c>
+      <c r="C22" s="2">
+        <v>72106</v>
+      </c>
+      <c r="D22" s="2">
+        <v>50444</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C23" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D23" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="B24" s="7">
-        <v>1896</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1899</v>
+      </c>
+      <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B25" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="8">
-        <v>18552</v>
+        <v>1906</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="B26" s="7">
-        <v>1898</v>
+        <v>1896</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C27" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D27" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="8">
+        <v>18552</v>
+      </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B28" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="8">
-        <v>16816</v>
+        <v>1898</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="E28" s="4"/>
     </row>
@@ -1018,95 +1020,93 @@
         <v>36</v>
       </c>
       <c r="B29" s="7">
-        <v>1892</v>
-      </c>
-      <c r="D29" s="8">
-        <v>19117</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C29" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D29" s="4"/>
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B30" s="7">
         <v>1886</v>
       </c>
-      <c r="C30" s="2">
-        <v>20065</v>
-      </c>
+      <c r="C30" s="2"/>
       <c r="D30" s="8">
-        <v>12678</v>
+        <v>16816</v>
       </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B31" s="7">
-        <v>1887</v>
-      </c>
-      <c r="C31" s="2">
-        <v>20264</v>
+        <v>1892</v>
       </c>
       <c r="D31" s="8">
-        <v>14329</v>
+        <v>19117</v>
       </c>
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B32" s="7">
-        <v>1882</v>
+        <v>1886</v>
+      </c>
+      <c r="C32" s="2">
+        <v>20065</v>
       </c>
       <c r="D32" s="8">
-        <v>15122</v>
+        <v>12678</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B33" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>20</v>
+        <v>1887</v>
+      </c>
+      <c r="C33" s="2">
+        <v>20264</v>
+      </c>
+      <c r="D33" s="8">
+        <v>14329</v>
       </c>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="9">
-        <v>1881</v>
-      </c>
-      <c r="C34" s="10">
-        <v>49210</v>
-      </c>
-      <c r="D34" s="10">
-        <v>28501</v>
+        <v>35</v>
+      </c>
+      <c r="B34" s="7">
+        <v>1882</v>
+      </c>
+      <c r="D34" s="8">
+        <v>15122</v>
       </c>
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="9">
-        <v>1882</v>
-      </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10">
-        <v>35470</v>
+        <v>11</v>
+      </c>
+      <c r="B35" s="7">
+        <v>1911</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E35" s="4"/>
     </row>
@@ -1115,13 +1115,13 @@
         <v>55</v>
       </c>
       <c r="B36" s="9">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="C36" s="10">
-        <v>60508</v>
+        <v>49210</v>
       </c>
       <c r="D36" s="10">
-        <v>34538</v>
+        <v>28501</v>
       </c>
       <c r="E36" s="4"/>
     </row>
@@ -1130,13 +1130,11 @@
         <v>55</v>
       </c>
       <c r="B37" s="9">
-        <v>1885</v>
-      </c>
-      <c r="C37" s="10">
-        <v>62341</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C37" s="10"/>
       <c r="D37" s="10">
-        <v>34345</v>
+        <v>35470</v>
       </c>
       <c r="E37" s="4"/>
     </row>
@@ -1145,13 +1143,13 @@
         <v>55</v>
       </c>
       <c r="B38" s="9">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="C38" s="10">
-        <v>62210</v>
+        <v>60508</v>
       </c>
       <c r="D38" s="10">
-        <v>34249</v>
+        <v>34538</v>
       </c>
       <c r="E38" s="4"/>
     </row>
@@ -1160,13 +1158,13 @@
         <v>55</v>
       </c>
       <c r="B39" s="9">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="C39" s="10">
-        <v>64897</v>
+        <v>62341</v>
       </c>
       <c r="D39" s="10">
-        <v>31536</v>
+        <v>34345</v>
       </c>
       <c r="E39" s="4"/>
     </row>
@@ -1175,13 +1173,13 @@
         <v>55</v>
       </c>
       <c r="B40" s="9">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="C40" s="10">
-        <v>67462</v>
+        <v>62210</v>
       </c>
       <c r="D40" s="10">
-        <v>39784</v>
+        <v>34249</v>
       </c>
       <c r="E40" s="4"/>
     </row>
@@ -1190,13 +1188,13 @@
         <v>55</v>
       </c>
       <c r="B41" s="9">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="C41" s="10">
-        <v>67604</v>
+        <v>64897</v>
       </c>
       <c r="D41" s="10">
-        <v>38492</v>
+        <v>31536</v>
       </c>
       <c r="E41" s="4"/>
     </row>
@@ -1205,13 +1203,13 @@
         <v>55</v>
       </c>
       <c r="B42" s="9">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="C42" s="10">
-        <v>69629</v>
+        <v>67462</v>
       </c>
       <c r="D42" s="10">
-        <v>39201</v>
+        <v>39784</v>
       </c>
       <c r="E42" s="4"/>
     </row>
@@ -1220,13 +1218,13 @@
         <v>55</v>
       </c>
       <c r="B43" s="9">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="C43" s="10">
-        <v>69629</v>
+        <v>67604</v>
       </c>
       <c r="D43" s="10">
-        <v>39201</v>
+        <v>38492</v>
       </c>
       <c r="E43" s="4"/>
     </row>
@@ -1235,12 +1233,14 @@
         <v>55</v>
       </c>
       <c r="B44" s="9">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="C44" s="10">
-        <v>77946</v>
-      </c>
-      <c r="D44" s="10"/>
+        <v>69629</v>
+      </c>
+      <c r="D44" s="10">
+        <v>39201</v>
+      </c>
       <c r="E44" s="4"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1248,13 +1248,13 @@
         <v>55</v>
       </c>
       <c r="B45" s="9">
-        <v>1895</v>
+        <v>1891</v>
       </c>
       <c r="C45" s="10">
-        <v>87026</v>
+        <v>69629</v>
       </c>
       <c r="D45" s="10">
-        <v>50346</v>
+        <v>39201</v>
       </c>
       <c r="E45" s="4"/>
     </row>
@@ -1263,14 +1263,12 @@
         <v>55</v>
       </c>
       <c r="B46" s="9">
-        <v>1896</v>
+        <v>1892</v>
       </c>
       <c r="C46" s="10">
-        <v>97843</v>
-      </c>
-      <c r="D46" s="10">
-        <v>57231</v>
-      </c>
+        <v>77946</v>
+      </c>
+      <c r="D46" s="10"/>
       <c r="E46" s="4"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1278,13 +1276,13 @@
         <v>55</v>
       </c>
       <c r="B47" s="9">
-        <v>1902</v>
+        <v>1895</v>
       </c>
       <c r="C47" s="10">
-        <v>117750</v>
+        <v>87026</v>
       </c>
       <c r="D47" s="10">
-        <v>65540</v>
+        <v>50346</v>
       </c>
       <c r="E47" s="4"/>
     </row>
@@ -1293,13 +1291,13 @@
         <v>55</v>
       </c>
       <c r="B48" s="9">
-        <v>1905</v>
+        <v>1896</v>
       </c>
       <c r="C48" s="10">
-        <v>113188</v>
+        <v>97843</v>
       </c>
       <c r="D48" s="10">
-        <v>76176</v>
+        <v>57231</v>
       </c>
       <c r="E48" s="4"/>
     </row>
@@ -1308,108 +1306,112 @@
         <v>55</v>
       </c>
       <c r="B49" s="9">
-        <v>1910</v>
+        <v>1902</v>
       </c>
       <c r="C49" s="10">
-        <v>209694</v>
-      </c>
-      <c r="D49" s="10"/>
+        <v>117750</v>
+      </c>
+      <c r="D49" s="10">
+        <v>65540</v>
+      </c>
       <c r="E49" s="4"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="7">
-        <v>1895</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>20</v>
+        <v>55</v>
+      </c>
+      <c r="B50" s="9">
+        <v>1905</v>
+      </c>
+      <c r="C50" s="10">
+        <v>113188</v>
+      </c>
+      <c r="D50" s="10">
+        <v>76176</v>
       </c>
       <c r="E50" s="4"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B51" s="9">
+        <v>1910</v>
+      </c>
+      <c r="C51" s="10">
+        <v>209694</v>
+      </c>
+      <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B52" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C52" s="8">
-        <v>94421</v>
-      </c>
-      <c r="D52" s="8">
-        <v>73778</v>
+        <v>1895</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B53" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C53" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F53" t="s">
-        <v>25</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="4"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B54" s="7">
         <v>1881</v>
       </c>
-      <c r="C54" s="2">
-        <v>88569</v>
-      </c>
+      <c r="C54" s="8">
+        <v>94421</v>
+      </c>
+      <c r="D54" s="8">
+        <v>73778</v>
+      </c>
+      <c r="E54" s="4"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B55" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2">
-        <v>5330</v>
+        <v>1901</v>
+      </c>
+      <c r="C55" s="2">
+        <v>103114</v>
+      </c>
+      <c r="F55" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B56" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D56" s="2">
-        <v>5235</v>
+        <v>1881</v>
+      </c>
+      <c r="C56" s="2">
+        <v>88569</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1417,37 +1419,33 @@
         <v>13</v>
       </c>
       <c r="B57" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" s="4"/>
+        <v>1881</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2">
+        <v>5330</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>13</v>
       </c>
       <c r="B58" s="7">
-        <v>1907</v>
+        <v>1882</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E58" s="4"/>
+      <c r="D58" s="2">
+        <v>5235</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>13</v>
       </c>
       <c r="B59" s="7">
-        <v>1913</v>
+        <v>1904</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>20</v>
@@ -1459,41 +1457,43 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B60" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E60" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F60" t="s">
-        <v>31</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="4"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B61" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E61" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F61" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="4"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>30</v>
       </c>
       <c r="B62" s="7">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="E62" s="2">
-        <v>603000</v>
+        <v>575000</v>
       </c>
       <c r="F62" t="s">
         <v>31</v>
@@ -1504,10 +1504,10 @@
         <v>30</v>
       </c>
       <c r="B63" s="7">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="E63" s="2">
-        <v>618000</v>
+        <v>589000</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -1518,10 +1518,10 @@
         <v>30</v>
       </c>
       <c r="B64" s="7">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="E64" s="2">
-        <v>633000</v>
+        <v>603000</v>
       </c>
       <c r="F64" t="s">
         <v>31</v>
@@ -1532,10 +1532,10 @@
         <v>30</v>
       </c>
       <c r="B65" s="7">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="E65" s="2">
-        <v>648000</v>
+        <v>618000</v>
       </c>
       <c r="F65" t="s">
         <v>31</v>
@@ -1546,10 +1546,10 @@
         <v>30</v>
       </c>
       <c r="B66" s="7">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="E66" s="2">
-        <v>664000</v>
+        <v>633000</v>
       </c>
       <c r="F66" t="s">
         <v>31</v>
@@ -1557,78 +1557,70 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B67" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C67" s="2">
-        <v>100871</v>
-      </c>
-      <c r="D67" s="2">
-        <v>79202</v>
+        <v>1886</v>
       </c>
       <c r="E67" s="2">
-        <v>2472605</v>
+        <v>648000</v>
       </c>
       <c r="F67" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="7"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
+      <c r="A68" t="s">
+        <v>30</v>
+      </c>
+      <c r="B68" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E68" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B69" s="7">
         <v>1914</v>
       </c>
       <c r="C69" s="2">
-        <v>60509</v>
+        <v>100871</v>
       </c>
       <c r="D69" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E69" s="2"/>
+        <v>79202</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2472605</v>
+      </c>
       <c r="F69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C70" s="2">
-        <v>62023</v>
-      </c>
-      <c r="D70" s="2">
-        <v>35541</v>
-      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-      <c r="F70" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B71" s="7">
         <v>1914</v>
       </c>
       <c r="C71" s="2">
-        <v>51346</v>
+        <v>60509</v>
       </c>
       <c r="D71" s="2">
-        <v>31414</v>
+        <v>34087</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s">
@@ -1637,16 +1629,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B72" s="7">
         <v>1914</v>
       </c>
       <c r="C72" s="2">
-        <v>14341</v>
+        <v>62023</v>
       </c>
       <c r="D72" s="2">
-        <v>11957</v>
+        <v>35541</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s">
@@ -1655,16 +1647,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B73" s="7">
         <v>1914</v>
       </c>
       <c r="C73" s="2">
-        <v>142692</v>
+        <v>51346</v>
       </c>
       <c r="D73" s="2">
-        <v>82123</v>
+        <v>31414</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s">
@@ -1672,79 +1664,91 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="7"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
+      <c r="A74" t="s">
+        <v>42</v>
+      </c>
+      <c r="B74" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C74" s="2">
+        <v>14341</v>
+      </c>
+      <c r="D74" s="2">
+        <v>11957</v>
+      </c>
       <c r="E74" s="2"/>
+      <c r="F74" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="7"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+      <c r="A75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B75" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C75" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D75" s="2">
+        <v>82123</v>
+      </c>
       <c r="E75" s="2"/>
+      <c r="F75" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="7"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="1" t="s">
+      <c r="B77" s="7"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" t="s">
         <v>24</v>
       </c>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="O85" s="3"/>
-      <c r="P85" s="2"/>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
-      <c r="O86" s="3"/>
-      <c r="P86" s="2"/>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
-      <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
       <c r="O87" s="3"/>
       <c r="P87" s="2"/>
     </row>
@@ -1767,6 +1771,8 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
       <c r="O89" s="3"/>
       <c r="P89" s="2"/>
     </row>
@@ -1777,14 +1783,10 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="O90" s="3"/>
       <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-      <c r="T90" s="2"/>
-      <c r="U90" s="2"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="2"/>
@@ -1793,6 +1795,8 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
+      <c r="O91" s="3"/>
+      <c r="P91" s="2"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="2"/>
@@ -1804,6 +1808,11 @@
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="2"/>
+      <c r="Q92" s="2"/>
+      <c r="T92" s="2"/>
+      <c r="U92" s="2"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="2"/>
@@ -1820,6 +1829,7 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
     </row>
@@ -1830,8 +1840,6 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="2"/>
@@ -1840,8 +1848,8 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
       <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
     </row>
     <row r="97" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="2"/>
@@ -1850,8 +1858,8 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
     </row>
     <row r="98" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="2"/>
@@ -1870,8 +1878,8 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
-      <c r="L99" s="2"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
     </row>
     <row r="100" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="2"/>
@@ -1880,8 +1888,8 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="2"/>
@@ -1900,7 +1908,8 @@
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
     </row>
     <row r="103" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="2"/>
@@ -1911,25 +1920,20 @@
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
-      <c r="O103" s="2"/>
     </row>
     <row r="104" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
+      <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
       <c r="O104" s="2"/>
     </row>
     <row r="105" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
+      <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
@@ -1938,14 +1942,32 @@
       <c r="O105" s="2"/>
     </row>
     <row r="106" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K106" s="6"/>
-      <c r="L106" s="6"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
       <c r="O106" s="2"/>
     </row>
     <row r="107" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
       <c r="O107" s="2"/>
     </row>
     <row r="108" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
       <c r="O108" s="2"/>
     </row>
     <row r="109" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1962,6 +1984,12 @@
     </row>
     <row r="113" spans="15:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O113" s="2"/>
+    </row>
+    <row r="114" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O114" s="2"/>
+    </row>
+    <row r="115" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O115" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EDC357-0B80-4F2F-9F61-AF6767D6EC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D34C739-FCCC-421F-9557-CF4D4DCB1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="59640" yWindow="1680" windowWidth="26595" windowHeight="18210" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="59">
   <si>
     <t>год</t>
   </si>
@@ -609,7 +609,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U115"/>
+  <dimension ref="A1:U118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -910,134 +910,133 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" s="7">
-        <v>1905</v>
-      </c>
-      <c r="C21" s="2">
-        <v>17694</v>
+        <v>1908</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2">
+        <v>2803</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" s="7">
-        <v>1881</v>
+        <v>1905</v>
       </c>
       <c r="C22" s="2">
-        <v>72106</v>
-      </c>
-      <c r="D22" s="2">
-        <v>50444</v>
-      </c>
+        <v>17694</v>
+      </c>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B23" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C23" s="2">
-        <v>47652</v>
-      </c>
+        <v>1908</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" s="2">
-        <v>28698</v>
+        <v>13046</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B24" s="7">
-        <v>1899</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="4"/>
+        <v>1881</v>
+      </c>
+      <c r="C24" s="2">
+        <v>72106</v>
+      </c>
+      <c r="D24" s="2">
+        <v>50444</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B25" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C25" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D25" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="B26" s="7">
-        <v>1896</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1899</v>
+      </c>
+      <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B27" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="8">
-        <v>18552</v>
+        <v>1906</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="B28" s="7">
-        <v>1898</v>
+        <v>1896</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C29" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D29" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="8">
+        <v>18552</v>
+      </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B30" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="8">
-        <v>16816</v>
+        <v>1898</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="E30" s="4"/>
     </row>
@@ -1046,95 +1045,93 @@
         <v>36</v>
       </c>
       <c r="B31" s="7">
-        <v>1892</v>
-      </c>
-      <c r="D31" s="8">
-        <v>19117</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C31" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D31" s="4"/>
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B32" s="7">
         <v>1886</v>
       </c>
-      <c r="C32" s="2">
-        <v>20065</v>
-      </c>
+      <c r="C32" s="2"/>
       <c r="D32" s="8">
-        <v>12678</v>
+        <v>16816</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B33" s="7">
-        <v>1887</v>
-      </c>
-      <c r="C33" s="2">
-        <v>20264</v>
+        <v>1892</v>
       </c>
       <c r="D33" s="8">
-        <v>14329</v>
+        <v>19117</v>
       </c>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B34" s="7">
-        <v>1882</v>
+        <v>1886</v>
+      </c>
+      <c r="C34" s="2">
+        <v>20065</v>
       </c>
       <c r="D34" s="8">
-        <v>15122</v>
+        <v>12678</v>
       </c>
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B35" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>20</v>
+        <v>1887</v>
+      </c>
+      <c r="C35" s="2">
+        <v>20264</v>
+      </c>
+      <c r="D35" s="8">
+        <v>14329</v>
       </c>
       <c r="E35" s="4"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="9">
-        <v>1881</v>
-      </c>
-      <c r="C36" s="10">
-        <v>49210</v>
-      </c>
-      <c r="D36" s="10">
-        <v>28501</v>
+        <v>35</v>
+      </c>
+      <c r="B36" s="7">
+        <v>1882</v>
+      </c>
+      <c r="D36" s="8">
+        <v>15122</v>
       </c>
       <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="9">
-        <v>1882</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10">
-        <v>35470</v>
+        <v>11</v>
+      </c>
+      <c r="B37" s="7">
+        <v>1911</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E37" s="4"/>
     </row>
@@ -1143,13 +1140,13 @@
         <v>55</v>
       </c>
       <c r="B38" s="9">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="C38" s="10">
-        <v>60508</v>
+        <v>49210</v>
       </c>
       <c r="D38" s="10">
-        <v>34538</v>
+        <v>28501</v>
       </c>
       <c r="E38" s="4"/>
     </row>
@@ -1158,13 +1155,11 @@
         <v>55</v>
       </c>
       <c r="B39" s="9">
-        <v>1885</v>
-      </c>
-      <c r="C39" s="10">
-        <v>62341</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C39" s="10"/>
       <c r="D39" s="10">
-        <v>34345</v>
+        <v>35470</v>
       </c>
       <c r="E39" s="4"/>
     </row>
@@ -1173,13 +1168,13 @@
         <v>55</v>
       </c>
       <c r="B40" s="9">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="C40" s="10">
-        <v>62210</v>
+        <v>60508</v>
       </c>
       <c r="D40" s="10">
-        <v>34249</v>
+        <v>34538</v>
       </c>
       <c r="E40" s="4"/>
     </row>
@@ -1188,13 +1183,13 @@
         <v>55</v>
       </c>
       <c r="B41" s="9">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="C41" s="10">
-        <v>64897</v>
+        <v>62341</v>
       </c>
       <c r="D41" s="10">
-        <v>31536</v>
+        <v>34345</v>
       </c>
       <c r="E41" s="4"/>
     </row>
@@ -1203,13 +1198,13 @@
         <v>55</v>
       </c>
       <c r="B42" s="9">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="C42" s="10">
-        <v>67462</v>
+        <v>62210</v>
       </c>
       <c r="D42" s="10">
-        <v>39784</v>
+        <v>34249</v>
       </c>
       <c r="E42" s="4"/>
     </row>
@@ -1218,13 +1213,13 @@
         <v>55</v>
       </c>
       <c r="B43" s="9">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="C43" s="10">
-        <v>67604</v>
+        <v>64897</v>
       </c>
       <c r="D43" s="10">
-        <v>38492</v>
+        <v>31536</v>
       </c>
       <c r="E43" s="4"/>
     </row>
@@ -1233,13 +1228,13 @@
         <v>55</v>
       </c>
       <c r="B44" s="9">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="C44" s="10">
-        <v>69629</v>
+        <v>67462</v>
       </c>
       <c r="D44" s="10">
-        <v>39201</v>
+        <v>39784</v>
       </c>
       <c r="E44" s="4"/>
     </row>
@@ -1248,13 +1243,13 @@
         <v>55</v>
       </c>
       <c r="B45" s="9">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="C45" s="10">
-        <v>69629</v>
+        <v>67604</v>
       </c>
       <c r="D45" s="10">
-        <v>39201</v>
+        <v>38492</v>
       </c>
       <c r="E45" s="4"/>
     </row>
@@ -1263,12 +1258,14 @@
         <v>55</v>
       </c>
       <c r="B46" s="9">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="C46" s="10">
-        <v>77946</v>
-      </c>
-      <c r="D46" s="10"/>
+        <v>69629</v>
+      </c>
+      <c r="D46" s="10">
+        <v>39201</v>
+      </c>
       <c r="E46" s="4"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1276,13 +1273,13 @@
         <v>55</v>
       </c>
       <c r="B47" s="9">
-        <v>1895</v>
+        <v>1891</v>
       </c>
       <c r="C47" s="10">
-        <v>87026</v>
+        <v>69629</v>
       </c>
       <c r="D47" s="10">
-        <v>50346</v>
+        <v>39201</v>
       </c>
       <c r="E47" s="4"/>
     </row>
@@ -1291,14 +1288,12 @@
         <v>55</v>
       </c>
       <c r="B48" s="9">
-        <v>1896</v>
+        <v>1892</v>
       </c>
       <c r="C48" s="10">
-        <v>97843</v>
-      </c>
-      <c r="D48" s="10">
-        <v>57231</v>
-      </c>
+        <v>77946</v>
+      </c>
+      <c r="D48" s="10"/>
       <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1306,13 +1301,13 @@
         <v>55</v>
       </c>
       <c r="B49" s="9">
-        <v>1902</v>
+        <v>1895</v>
       </c>
       <c r="C49" s="10">
-        <v>117750</v>
+        <v>87026</v>
       </c>
       <c r="D49" s="10">
-        <v>65540</v>
+        <v>50346</v>
       </c>
       <c r="E49" s="4"/>
     </row>
@@ -1321,13 +1316,13 @@
         <v>55</v>
       </c>
       <c r="B50" s="9">
-        <v>1905</v>
+        <v>1896</v>
       </c>
       <c r="C50" s="10">
-        <v>113188</v>
+        <v>97843</v>
       </c>
       <c r="D50" s="10">
-        <v>76176</v>
+        <v>57231</v>
       </c>
       <c r="E50" s="4"/>
     </row>
@@ -1336,206 +1331,206 @@
         <v>55</v>
       </c>
       <c r="B51" s="9">
-        <v>1910</v>
+        <v>1902</v>
       </c>
       <c r="C51" s="10">
-        <v>209694</v>
-      </c>
-      <c r="D51" s="10"/>
+        <v>117750</v>
+      </c>
+      <c r="D51" s="10">
+        <v>65540</v>
+      </c>
       <c r="E51" s="4"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="7">
-        <v>1895</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>20</v>
+        <v>55</v>
+      </c>
+      <c r="B52" s="9">
+        <v>1905</v>
+      </c>
+      <c r="C52" s="10">
+        <v>113188</v>
+      </c>
+      <c r="D52" s="10">
+        <v>76176</v>
       </c>
       <c r="E52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B53" s="9">
+        <v>1910</v>
+      </c>
+      <c r="C53" s="10">
+        <v>209694</v>
+      </c>
+      <c r="D53" s="10"/>
       <c r="E53" s="4"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B54" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C54" s="8">
-        <v>94421</v>
-      </c>
-      <c r="D54" s="8">
-        <v>73778</v>
+        <v>1895</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E54" s="4"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B55" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C55" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F55" t="s">
-        <v>25</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B56" s="7">
         <v>1881</v>
       </c>
-      <c r="C56" s="2">
-        <v>88569</v>
-      </c>
+      <c r="C56" s="8">
+        <v>94421</v>
+      </c>
+      <c r="D56" s="8">
+        <v>73778</v>
+      </c>
+      <c r="E56" s="4"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2">
-        <v>5330</v>
+        <v>1901</v>
+      </c>
+      <c r="C57" s="2">
+        <v>103114</v>
+      </c>
+      <c r="F57" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1908</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" s="2">
-        <v>5235</v>
+        <v>70106</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B59" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="4"/>
+        <v>1881</v>
+      </c>
+      <c r="C59" s="2">
+        <v>88569</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>13</v>
       </c>
       <c r="B60" s="7">
-        <v>1907</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" s="4"/>
+        <v>1881</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2">
+        <v>5330</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>13</v>
       </c>
       <c r="B61" s="7">
-        <v>1913</v>
+        <v>1882</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="4"/>
+      <c r="D61" s="2">
+        <v>5235</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B62" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E62" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F62" t="s">
-        <v>31</v>
-      </c>
+        <v>1904</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="4"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B63" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E63" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F63" t="s">
-        <v>31</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="4"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B64" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E64" s="2">
-        <v>603000</v>
-      </c>
-      <c r="F64" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="4"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>30</v>
       </c>
       <c r="B65" s="7">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="E65" s="2">
-        <v>618000</v>
+        <v>575000</v>
       </c>
       <c r="F65" t="s">
         <v>31</v>
@@ -1546,10 +1541,10 @@
         <v>30</v>
       </c>
       <c r="B66" s="7">
-        <v>1885</v>
+        <v>1882</v>
       </c>
       <c r="E66" s="2">
-        <v>633000</v>
+        <v>589000</v>
       </c>
       <c r="F66" t="s">
         <v>31</v>
@@ -1560,10 +1555,10 @@
         <v>30</v>
       </c>
       <c r="B67" s="7">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="E67" s="2">
-        <v>648000</v>
+        <v>603000</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -1574,10 +1569,10 @@
         <v>30</v>
       </c>
       <c r="B68" s="7">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="E68" s="2">
-        <v>664000</v>
+        <v>618000</v>
       </c>
       <c r="F68" t="s">
         <v>31</v>
@@ -1585,96 +1580,84 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B69" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C69" s="2">
-        <v>100871</v>
-      </c>
-      <c r="D69" s="2">
-        <v>79202</v>
+        <v>1885</v>
       </c>
       <c r="E69" s="2">
-        <v>2472605</v>
+        <v>633000</v>
       </c>
       <c r="F69" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="7"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+      <c r="A70" t="s">
+        <v>30</v>
+      </c>
+      <c r="B70" s="7">
+        <v>1886</v>
+      </c>
+      <c r="E70" s="2">
+        <v>648000</v>
+      </c>
+      <c r="F70" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B71" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C71" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D71" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E71" s="2"/>
+        <v>1887</v>
+      </c>
+      <c r="E71" s="2">
+        <v>664000</v>
+      </c>
       <c r="F71" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B72" s="7">
         <v>1914</v>
       </c>
       <c r="C72" s="2">
-        <v>62023</v>
+        <v>100871</v>
       </c>
       <c r="D72" s="2">
-        <v>35541</v>
-      </c>
-      <c r="E72" s="2"/>
+        <v>79202</v>
+      </c>
+      <c r="E72" s="2">
+        <v>2472605</v>
+      </c>
       <c r="F72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" t="s">
-        <v>41</v>
-      </c>
-      <c r="B73" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C73" s="2">
-        <v>51346</v>
-      </c>
-      <c r="D73" s="2">
-        <v>31414</v>
-      </c>
+      <c r="B73" s="7"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-      <c r="F73" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B74" s="7">
         <v>1914</v>
       </c>
       <c r="C74" s="2">
-        <v>14341</v>
+        <v>60509</v>
       </c>
       <c r="D74" s="2">
-        <v>11957</v>
+        <v>34087</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s">
@@ -1683,16 +1666,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B75" s="7">
         <v>1914</v>
       </c>
       <c r="C75" s="2">
-        <v>142692</v>
+        <v>62023</v>
       </c>
       <c r="D75" s="2">
-        <v>82123</v>
+        <v>35541</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s">
@@ -1700,91 +1683,109 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="7"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
+      <c r="A76" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C76" s="2">
+        <v>51346</v>
+      </c>
+      <c r="D76" s="2">
+        <v>31414</v>
+      </c>
       <c r="E76" s="2"/>
+      <c r="F76" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="7"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
+      <c r="A77" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C77" s="2">
+        <v>14341</v>
+      </c>
+      <c r="D77" s="2">
+        <v>11957</v>
+      </c>
       <c r="E77" s="2"/>
+      <c r="F77" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C78" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D78" s="2">
+        <v>82123</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="1" t="s">
+      <c r="B79" s="7"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="7"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" t="s">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" t="s">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" t="s">
         <v>24</v>
       </c>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="O87" s="3"/>
-      <c r="P87" s="2"/>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="O88" s="3"/>
-      <c r="P88" s="2"/>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-      <c r="O89" s="3"/>
-      <c r="P89" s="2"/>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
-      <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
       <c r="O90" s="3"/>
       <c r="P90" s="2"/>
     </row>
@@ -1795,6 +1796,8 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
       <c r="O91" s="3"/>
       <c r="P91" s="2"/>
     </row>
@@ -1805,14 +1808,10 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="O92" s="3"/>
       <c r="P92" s="2"/>
-      <c r="Q92" s="2"/>
-      <c r="T92" s="2"/>
-      <c r="U92" s="2"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="2"/>
@@ -1821,6 +1820,10 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+      <c r="O93" s="3"/>
+      <c r="P93" s="2"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="2"/>
@@ -1829,9 +1832,8 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="2"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="2"/>
@@ -1840,6 +1842,14 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="2"/>
+      <c r="Q95" s="2"/>
+      <c r="T95" s="2"/>
+      <c r="U95" s="2"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="2"/>
@@ -1848,8 +1858,6 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
     </row>
     <row r="97" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="2"/>
@@ -1860,6 +1868,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
+      <c r="M97" s="2"/>
     </row>
     <row r="98" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="2"/>
@@ -1868,8 +1877,6 @@
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
-      <c r="L98" s="2"/>
     </row>
     <row r="99" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="2"/>
@@ -1878,8 +1885,8 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2"/>
     </row>
     <row r="100" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="2"/>
@@ -1928,7 +1935,8 @@
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
-      <c r="O104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
     </row>
     <row r="105" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="2"/>
@@ -1937,46 +1945,66 @@
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
-      <c r="O105" s="2"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
     </row>
     <row r="106" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
+      <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
-      <c r="O106" s="2"/>
     </row>
     <row r="107" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
+      <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
       <c r="O107" s="2"/>
     </row>
     <row r="108" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
       <c r="O108" s="2"/>
     </row>
     <row r="109" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
       <c r="O109" s="2"/>
     </row>
     <row r="110" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
       <c r="O110" s="2"/>
     </row>
     <row r="111" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
       <c r="O111" s="2"/>
     </row>
     <row r="112" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1990,6 +2018,15 @@
     </row>
     <row r="115" spans="15:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O115" s="2"/>
+    </row>
+    <row r="116" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O116" s="2"/>
+    </row>
+    <row r="117" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O117" s="2"/>
+    </row>
+    <row r="118" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O118" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D34C739-FCCC-421F-9557-CF4D4DCB1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DC6058-CCA3-4EE5-A5C1-7922C5A95701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59640" yWindow="1680" windowWidth="26595" windowHeight="18210" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="59460" yWindow="1320" windowWidth="24750" windowHeight="18810" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="60">
   <si>
     <t>год</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>г. Одесса</t>
+  </si>
+  <si>
+    <t>Эриванская</t>
   </si>
 </sst>
 </file>
@@ -219,7 +222,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +237,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -256,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -280,6 +295,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,7 +628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U118"/>
+  <dimension ref="A1:U124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -1453,168 +1472,160 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>13</v>
-      </c>
-      <c r="B60" s="7">
-        <v>1881</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2">
-        <v>5330</v>
+        <v>59</v>
+      </c>
+      <c r="B60" s="11">
+        <v>1883</v>
+      </c>
+      <c r="C60" s="12">
+        <v>19909</v>
+      </c>
+      <c r="D60" s="12">
+        <v>13529</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D61" s="2">
-        <v>5235</v>
+        <v>59</v>
+      </c>
+      <c r="B61" s="11">
+        <v>1884</v>
+      </c>
+      <c r="C61" s="12">
+        <v>21625</v>
+      </c>
+      <c r="D61" s="12">
+        <v>11583</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>13</v>
-      </c>
-      <c r="B62" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="B62" s="11">
+        <v>1887</v>
+      </c>
+      <c r="C62" s="12">
+        <v>21202</v>
+      </c>
+      <c r="D62" s="12">
+        <v>11142</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>13</v>
-      </c>
-      <c r="B63" s="7">
-        <v>1907</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="B63" s="11">
+        <v>1888</v>
+      </c>
+      <c r="C63" s="12">
+        <v>25675</v>
+      </c>
+      <c r="D63" s="12">
+        <v>17262</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>13</v>
-      </c>
-      <c r="B64" s="7">
-        <v>1913</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="B64" s="11">
+        <v>1891</v>
+      </c>
+      <c r="C64" s="12">
+        <v>24293</v>
+      </c>
+      <c r="D64" s="12">
+        <v>13501</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B65" s="7">
         <v>1881</v>
       </c>
-      <c r="E65" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F65" t="s">
-        <v>31</v>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2">
+        <v>5330</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B66" s="7">
         <v>1882</v>
       </c>
-      <c r="E66" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F66" t="s">
-        <v>31</v>
+      <c r="C66" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="2">
+        <v>5235</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B67" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E67" s="2">
-        <v>603000</v>
-      </c>
-      <c r="F67" t="s">
-        <v>31</v>
-      </c>
+        <v>1904</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="4"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>1884</v>
-      </c>
-      <c r="E68" s="2">
-        <v>618000</v>
-      </c>
-      <c r="F68" t="s">
-        <v>31</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" s="4"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>1885</v>
-      </c>
-      <c r="E69" s="2">
-        <v>633000</v>
-      </c>
-      <c r="F69" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="4"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" t="s">
-        <v>30</v>
-      </c>
-      <c r="B70" s="7">
-        <v>1886</v>
-      </c>
-      <c r="E70" s="2">
-        <v>648000</v>
-      </c>
-      <c r="F70" t="s">
-        <v>31</v>
-      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>30</v>
       </c>
       <c r="B71" s="7">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="E71" s="2">
-        <v>664000</v>
+        <v>575000</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -1622,118 +1633,106 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B72" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C72" s="2">
-        <v>100871</v>
-      </c>
-      <c r="D72" s="2">
-        <v>79202</v>
+        <v>1882</v>
       </c>
       <c r="E72" s="2">
-        <v>2472605</v>
+        <v>589000</v>
       </c>
       <c r="F72" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="7"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
+      <c r="A73" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" s="7">
+        <v>1883</v>
+      </c>
+      <c r="E73" s="2">
+        <v>603000</v>
+      </c>
+      <c r="F73" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B74" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C74" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D74" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E74" s="2"/>
+        <v>1884</v>
+      </c>
+      <c r="E74" s="2">
+        <v>618000</v>
+      </c>
       <c r="F74" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B75" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C75" s="2">
-        <v>62023</v>
-      </c>
-      <c r="D75" s="2">
-        <v>35541</v>
-      </c>
-      <c r="E75" s="2"/>
+        <v>1885</v>
+      </c>
+      <c r="E75" s="2">
+        <v>633000</v>
+      </c>
       <c r="F75" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B76" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C76" s="2">
-        <v>51346</v>
-      </c>
-      <c r="D76" s="2">
-        <v>31414</v>
-      </c>
-      <c r="E76" s="2"/>
+        <v>1886</v>
+      </c>
+      <c r="E76" s="2">
+        <v>648000</v>
+      </c>
       <c r="F76" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B77" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C77" s="2">
-        <v>14341</v>
-      </c>
-      <c r="D77" s="2">
-        <v>11957</v>
-      </c>
-      <c r="E77" s="2"/>
+        <v>1887</v>
+      </c>
+      <c r="E77" s="2">
+        <v>664000</v>
+      </c>
       <c r="F77" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B78" s="7">
         <v>1914</v>
       </c>
       <c r="C78" s="2">
-        <v>142692</v>
+        <v>100871</v>
       </c>
       <c r="D78" s="2">
-        <v>82123</v>
-      </c>
-      <c r="E78" s="2"/>
+        <v>79202</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2472605</v>
+      </c>
       <c r="F78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1743,142 +1742,173 @@
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="7"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
+      <c r="A80" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C80" s="2">
+        <v>60509</v>
+      </c>
+      <c r="D80" s="2">
+        <v>34087</v>
+      </c>
       <c r="E80" s="2"/>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="1" t="s">
+      <c r="F80" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C81" s="2">
+        <v>62023</v>
+      </c>
+      <c r="D81" s="2">
+        <v>35541</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>41</v>
+      </c>
+      <c r="B82" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C82" s="2">
+        <v>51346</v>
+      </c>
+      <c r="D82" s="2">
+        <v>31414</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" t="s">
+        <v>42</v>
+      </c>
+      <c r="B83" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C83" s="2">
+        <v>14341</v>
+      </c>
+      <c r="D83" s="2">
+        <v>11957</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C84" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D84" s="2">
+        <v>82123</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="7"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="7"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" t="s">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" t="s">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" t="s">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" t="s">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" t="s">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" t="s">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
         <v>24</v>
       </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="O90" s="3"/>
-      <c r="P90" s="2"/>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-      <c r="O91" s="3"/>
-      <c r="P91" s="2"/>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
-      <c r="O92" s="3"/>
-      <c r="P92" s="2"/>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
-      <c r="O93" s="3"/>
-      <c r="P93" s="2"/>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="O94" s="3"/>
-      <c r="P94" s="2"/>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="O95" s="3"/>
-      <c r="P95" s="2"/>
-      <c r="Q95" s="2"/>
-      <c r="T95" s="2"/>
-      <c r="U95" s="2"/>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
-      <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-    </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O96" s="3"/>
+      <c r="P96" s="2"/>
+    </row>
+    <row r="97" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
-    </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O97" s="3"/>
+      <c r="P97" s="2"/>
+    </row>
+    <row r="98" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
-    </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="2"/>
+    </row>
+    <row r="99" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="G99" s="2"/>
@@ -1887,18 +1917,20 @@
       <c r="J99" s="2"/>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
-    </row>
-    <row r="100" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O99" s="3"/>
+      <c r="P99" s="2"/>
+    </row>
+    <row r="100" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
-    </row>
-    <row r="101" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O100" s="3"/>
+      <c r="P100" s="2"/>
+    </row>
+    <row r="101" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="G101" s="2"/>
@@ -1907,18 +1939,22 @@
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
-    </row>
-    <row r="102" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="M101" s="2"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
+      <c r="T101" s="2"/>
+      <c r="U101" s="2"/>
+    </row>
+    <row r="102" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-    </row>
-    <row r="103" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="103" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="G103" s="2"/>
@@ -1927,28 +1963,27 @@
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
-    </row>
-    <row r="104" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="M103" s="2"/>
+    </row>
+    <row r="104" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
-    </row>
-    <row r="105" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="105" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
-    </row>
-    <row r="106" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
+    </row>
+    <row r="106" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="G106" s="2"/>
@@ -1958,75 +1993,135 @@
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
-    <row r="107" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
-      <c r="O107" s="2"/>
-    </row>
-    <row r="108" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+    </row>
+    <row r="108" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
-      <c r="O108" s="2"/>
-    </row>
-    <row r="109" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+    </row>
+    <row r="109" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
+      <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
-      <c r="O109" s="2"/>
-    </row>
-    <row r="110" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="110" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
+      <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
-      <c r="O110" s="2"/>
-    </row>
-    <row r="111" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="111" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
       <c r="K111" s="6"/>
       <c r="L111" s="6"/>
-      <c r="O111" s="2"/>
-    </row>
-    <row r="112" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O112" s="2"/>
-    </row>
-    <row r="113" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="112" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
+    </row>
+    <row r="113" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
       <c r="O113" s="2"/>
     </row>
-    <row r="114" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
       <c r="O114" s="2"/>
     </row>
-    <row r="115" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
       <c r="O115" s="2"/>
     </row>
-    <row r="116" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
       <c r="O116" s="2"/>
     </row>
-    <row r="117" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
       <c r="O117" s="2"/>
     </row>
-    <row r="118" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O118" s="2"/>
+    </row>
+    <row r="119" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O119" s="2"/>
+    </row>
+    <row r="120" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O120" s="2"/>
+    </row>
+    <row r="121" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O121" s="2"/>
+    </row>
+    <row r="122" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O122" s="2"/>
+    </row>
+    <row r="123" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O123" s="2"/>
+    </row>
+    <row r="124" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O124" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DC6058-CCA3-4EE5-A5C1-7922C5A95701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13784564-747D-40D6-8C7D-7EF2BE9FDF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59460" yWindow="1320" windowWidth="24750" windowHeight="18810" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="60">
   <si>
     <t>год</t>
   </si>
@@ -628,7 +628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U124"/>
+  <dimension ref="A1:U129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.26171875" customWidth="1"/>
@@ -1571,131 +1571,131 @@
         <v>13</v>
       </c>
       <c r="B67" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="4"/>
+        <v>1886</v>
+      </c>
+      <c r="C67" s="8">
+        <v>8714</v>
+      </c>
+      <c r="D67" s="2">
+        <v>6138</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>1907</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E68" s="4"/>
+        <v>1887</v>
+      </c>
+      <c r="C68" s="8">
+        <v>8433</v>
+      </c>
+      <c r="D68" s="2">
+        <v>7262</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>1913</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="4"/>
+        <v>1888</v>
+      </c>
+      <c r="C69" s="8">
+        <v>8889</v>
+      </c>
+      <c r="D69" s="2">
+        <v>6799</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="7"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
+      <c r="A70" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70" s="7">
+        <v>1889</v>
+      </c>
+      <c r="C70" s="8">
+        <v>9512</v>
+      </c>
+      <c r="D70" s="2">
+        <v>10525</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B71" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E71" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F71" t="s">
-        <v>31</v>
+        <v>1890</v>
+      </c>
+      <c r="C71" s="8">
+        <v>10481</v>
+      </c>
+      <c r="D71" s="2">
+        <v>6502</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B72" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E72" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F72" t="s">
-        <v>31</v>
-      </c>
+        <v>1904</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B73" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E73" s="2">
-        <v>603000</v>
-      </c>
-      <c r="F73" t="s">
-        <v>31</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B74" s="7">
-        <v>1884</v>
-      </c>
-      <c r="E74" s="2">
-        <v>618000</v>
-      </c>
-      <c r="F74" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" s="4"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" t="s">
-        <v>30</v>
-      </c>
-      <c r="B75" s="7">
-        <v>1885</v>
-      </c>
-      <c r="E75" s="2">
-        <v>633000</v>
-      </c>
-      <c r="F75" t="s">
-        <v>31</v>
-      </c>
+      <c r="B75" s="7"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>30</v>
       </c>
       <c r="B76" s="7">
-        <v>1886</v>
+        <v>1881</v>
       </c>
       <c r="E76" s="2">
-        <v>648000</v>
+        <v>575000</v>
       </c>
       <c r="F76" t="s">
         <v>31</v>
@@ -1706,10 +1706,10 @@
         <v>30</v>
       </c>
       <c r="B77" s="7">
-        <v>1887</v>
+        <v>1882</v>
       </c>
       <c r="E77" s="2">
-        <v>664000</v>
+        <v>589000</v>
       </c>
       <c r="F77" t="s">
         <v>31</v>
@@ -1717,273 +1717,290 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B78" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C78" s="2">
-        <v>100871</v>
-      </c>
-      <c r="D78" s="2">
-        <v>79202</v>
+        <v>1883</v>
       </c>
       <c r="E78" s="2">
-        <v>2472605</v>
+        <v>603000</v>
       </c>
       <c r="F78" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="7"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
+      <c r="A79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79" s="7">
+        <v>1884</v>
+      </c>
+      <c r="E79" s="2">
+        <v>618000</v>
+      </c>
+      <c r="F79" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B80" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C80" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D80" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E80" s="2"/>
+        <v>1885</v>
+      </c>
+      <c r="E80" s="2">
+        <v>633000</v>
+      </c>
       <c r="F80" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B81" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C81" s="2">
-        <v>62023</v>
-      </c>
-      <c r="D81" s="2">
-        <v>35541</v>
-      </c>
-      <c r="E81" s="2"/>
+        <v>1886</v>
+      </c>
+      <c r="E81" s="2">
+        <v>648000</v>
+      </c>
       <c r="F81" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B82" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C82" s="2">
-        <v>51346</v>
-      </c>
-      <c r="D82" s="2">
-        <v>31414</v>
-      </c>
-      <c r="E82" s="2"/>
+        <v>1887</v>
+      </c>
+      <c r="E82" s="2">
+        <v>664000</v>
+      </c>
       <c r="F82" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B83" s="7">
         <v>1914</v>
       </c>
       <c r="C83" s="2">
+        <v>100871</v>
+      </c>
+      <c r="D83" s="2">
+        <v>79202</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2472605</v>
+      </c>
+      <c r="F83" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="7"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C85" s="2">
+        <v>60509</v>
+      </c>
+      <c r="D85" s="2">
+        <v>34087</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C86" s="2">
+        <v>62023</v>
+      </c>
+      <c r="D86" s="2">
+        <v>35541</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" t="s">
+        <v>41</v>
+      </c>
+      <c r="B87" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C87" s="2">
+        <v>51346</v>
+      </c>
+      <c r="D87" s="2">
+        <v>31414</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B88" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C88" s="2">
         <v>14341</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D88" s="2">
         <v>11957</v>
       </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s">
+      <c r="E88" s="2"/>
+      <c r="F88" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" t="s">
         <v>43</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B89" s="7">
         <v>1914</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C89" s="2">
         <v>142692</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D89" s="2">
         <v>82123</v>
       </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s">
+      <c r="E89" s="2"/>
+      <c r="F89" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="7"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="7"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="1" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="7"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="7"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" t="s">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" t="s">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" t="s">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" t="s">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" t="s">
         <v>24</v>
       </c>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="O96" s="3"/>
-      <c r="P96" s="2"/>
-    </row>
-    <row r="97" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="L97" s="2"/>
-      <c r="M97" s="2"/>
-      <c r="O97" s="3"/>
-      <c r="P97" s="2"/>
-    </row>
-    <row r="98" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-      <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
-      <c r="O98" s="3"/>
-      <c r="P98" s="2"/>
-    </row>
-    <row r="99" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
-      <c r="O99" s="3"/>
-      <c r="P99" s="2"/>
-    </row>
-    <row r="100" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="O100" s="3"/>
-      <c r="P100" s="2"/>
-    </row>
-    <row r="101" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
-      <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
-      <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
       <c r="O101" s="3"/>
       <c r="P101" s="2"/>
-      <c r="Q101" s="2"/>
-      <c r="T101" s="2"/>
-      <c r="U101" s="2"/>
-    </row>
-    <row r="102" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
-    </row>
-    <row r="103" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="L102" s="2"/>
+      <c r="M102" s="2"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="2"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
-    </row>
-    <row r="104" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="O103" s="3"/>
+      <c r="P103" s="2"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
-    </row>
-    <row r="105" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="L104" s="2"/>
+      <c r="M104" s="2"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="2"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
-      <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
-    </row>
-    <row r="106" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="O105" s="3"/>
+      <c r="P105" s="2"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="G106" s="2"/>
@@ -1992,58 +2009,61 @@
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
-    </row>
-    <row r="107" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M106" s="2"/>
+      <c r="O106" s="3"/>
+      <c r="P106" s="2"/>
+      <c r="Q106" s="2"/>
+      <c r="T106" s="2"/>
+      <c r="U106" s="2"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
-    </row>
-    <row r="108" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-    </row>
-    <row r="109" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
-      <c r="K109" s="2"/>
-      <c r="L109" s="2"/>
-    </row>
-    <row r="110" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
-      <c r="K110" s="2"/>
       <c r="L110" s="2"/>
-    </row>
-    <row r="111" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M110" s="2"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
-    </row>
-    <row r="112" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="G112" s="2"/>
@@ -2060,7 +2080,8 @@
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
-      <c r="O113" s="2"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
     </row>
     <row r="114" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" s="2"/>
@@ -2071,50 +2092,84 @@
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
-      <c r="O114" s="2"/>
     </row>
     <row r="115" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
+      <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
-      <c r="O115" s="2"/>
     </row>
     <row r="116" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
+      <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
-      <c r="L116" s="2"/>
-      <c r="O116" s="2"/>
+      <c r="K116" s="6"/>
+      <c r="L116" s="6"/>
     </row>
     <row r="117" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K117" s="6"/>
-      <c r="L117" s="6"/>
-      <c r="O117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
     </row>
     <row r="118" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
       <c r="O118" s="2"/>
     </row>
     <row r="119" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
       <c r="O119" s="2"/>
     </row>
     <row r="120" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
       <c r="O120" s="2"/>
     </row>
     <row r="121" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
       <c r="O121" s="2"/>
     </row>
     <row r="122" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K122" s="6"/>
+      <c r="L122" s="6"/>
       <c r="O122" s="2"/>
     </row>
     <row r="123" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -2122,6 +2177,21 @@
     </row>
     <row r="124" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O124" s="2"/>
+    </row>
+    <row r="125" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O125" s="2"/>
+    </row>
+    <row r="126" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O126" s="2"/>
+    </row>
+    <row r="127" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O127" s="2"/>
+    </row>
+    <row r="128" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O128" s="2"/>
+    </row>
+    <row r="129" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O129" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
